--- a/src/attributions/attributions_ig_traj_81.xlsx
+++ b/src/attributions/attributions_ig_traj_81.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GG14"/>
+  <dimension ref="A1:GG15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -999,10 +999,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.4040280904317399</v>
+        <v>0.1359497992411656</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -1011,25 +1011,25 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.01000848749638597</v>
+        <v>-0.03420086452153837</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.158535578047521</v>
+        <v>-0.0537389098460636</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K2" t="n">
-        <v>0.4112871118989492</v>
+        <v>0.2313156224028639</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -1038,7 +1038,7 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.04159222220009338</v>
+        <v>-0.0966282174877925</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -1047,16 +1047,16 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.2706157279754271</v>
+        <v>-0.09494582885867513</v>
       </c>
       <c r="S2" t="n">
         <v>-0</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1514208053356803</v>
+        <v>0.06006356981022789</v>
       </c>
       <c r="U2" t="n">
         <v>-0</v>
@@ -1065,106 +1065,106 @@
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0.09699626485459996</v>
+        <v>-0.06164469459279712</v>
       </c>
       <c r="X2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0.04881859833911845</v>
+        <v>-0.05158283471272526</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.1533162989669991</v>
+        <v>-0.06595817684902855</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.2045858398631362</v>
+        <v>-0.1065273433441691</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-0.07784202597128015</v>
+        <v>0.07005437614530063</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.1021165407394009</v>
+        <v>0.0604647339965094</v>
       </c>
       <c r="AM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
         <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>-0.00761390023272436</v>
+        <v>-0.008856936868732184</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>-0.04629308516694643</v>
+        <v>0.02781920081187647</v>
       </c>
       <c r="AT2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.2631480535683403</v>
+        <v>0.1182247626567902</v>
       </c>
       <c r="AV2" t="n">
         <v>-0</v>
       </c>
       <c r="AW2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.1175799566638133</v>
+        <v>-0.03660826754609459</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>-0.07126039823139134</v>
+        <v>-0.01948569287940114</v>
       </c>
       <c r="BC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.05348424580105621</v>
+        <v>-0.02457077536848706</v>
       </c>
       <c r="BE2" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="BG2" t="n">
-        <v>-0.1344198813216668</v>
+        <v>-0.05395007777742549</v>
       </c>
       <c r="BH2" t="n">
         <v>0</v>
@@ -1182,109 +1182,109 @@
         <v>-0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK2" t="n">
-        <v>-0.2128558466529914</v>
+        <v>-0.09748236078696426</v>
       </c>
       <c r="BL2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>-0.03582487539693634</v>
+        <v>0.01987413259543892</v>
       </c>
       <c r="BN2" t="n">
         <v>-0</v>
       </c>
       <c r="BO2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.3085802223927507</v>
+        <v>0.1428831957887373</v>
       </c>
       <c r="BQ2" t="n">
         <v>-0</v>
       </c>
       <c r="BR2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.0994361582550739</v>
+        <v>0.06632894884683987</v>
       </c>
       <c r="BU2" t="n">
         <v>-0</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.4257621950057804</v>
+        <v>0.1794065010653992</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX2" t="n">
         <v>0</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.09554615427542303</v>
+        <v>-0.05715212446191077</v>
       </c>
       <c r="BZ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC2" t="n">
-        <v>-0.05048885591892328</v>
+        <v>-0.08377691607369121</v>
       </c>
       <c r="CD2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE2" t="n">
-        <v>-0.1532720387635735</v>
+        <v>-0.09333305977912296</v>
       </c>
       <c r="CF2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG2" t="n">
         <v>-0</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.009337357976487866</v>
+        <v>0.0208087125075311</v>
       </c>
       <c r="CI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.1213226548525455</v>
+        <v>0.05152373540353596</v>
       </c>
       <c r="CM2" t="n">
         <v>0</v>
       </c>
       <c r="CN2" t="n">
-        <v>-0.03450033041561451</v>
+        <v>-0.1012813785331302</v>
       </c>
       <c r="CO2" t="n">
         <v>-0</v>
       </c>
       <c r="CP2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ2" t="n">
-        <v>-0.09574839461651867</v>
+        <v>0.03144304395493479</v>
       </c>
       <c r="CR2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS2" t="n">
         <v>-0</v>
@@ -1293,40 +1293,40 @@
         <v>-0</v>
       </c>
       <c r="CU2" t="n">
-        <v>0.022052191551602</v>
+        <v>0.04534353603902484</v>
       </c>
       <c r="CV2" t="n">
         <v>-0</v>
       </c>
       <c r="CW2" t="n">
-        <v>-0.1683696977703676</v>
+        <v>-0.09121345047186909</v>
       </c>
       <c r="CX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY2" t="n">
         <v>0</v>
       </c>
       <c r="CZ2" t="n">
-        <v>0.01425884418430298</v>
+        <v>0.005514800792461555</v>
       </c>
       <c r="DA2" t="n">
         <v>0</v>
       </c>
       <c r="DB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD2" t="n">
-        <v>0.08850130533265961</v>
+        <v>0.05823583328628926</v>
       </c>
       <c r="DE2" t="n">
         <v>0</v>
       </c>
       <c r="DF2" t="n">
-        <v>-0.1979961930535364</v>
+        <v>-0.1551580969320634</v>
       </c>
       <c r="DG2" t="n">
         <v>-0</v>
@@ -1335,52 +1335,52 @@
         <v>-0</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.02954969541894217</v>
+        <v>0.003178886167445221</v>
       </c>
       <c r="DJ2" t="n">
         <v>-0</v>
       </c>
       <c r="DK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL2" t="n">
         <v>0</v>
       </c>
       <c r="DM2" t="n">
-        <v>0.06275496052978354</v>
+        <v>0.006258169459298295</v>
       </c>
       <c r="DN2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO2" t="n">
-        <v>-0.07517854130798524</v>
+        <v>-0.06349347770698625</v>
       </c>
       <c r="DP2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ2" t="n">
         <v>0</v>
       </c>
       <c r="DR2" t="n">
-        <v>-0.1337129429475252</v>
+        <v>0.07784071416043011</v>
       </c>
       <c r="DS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>-0.06713495813326448</v>
+        <v>0.1107564018021523</v>
       </c>
       <c r="DW2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX2" t="n">
-        <v>-0.2084390528010975</v>
+        <v>-0.061831857046266</v>
       </c>
       <c r="DY2" t="n">
         <v>-0</v>
@@ -1389,10 +1389,10 @@
         <v>-0</v>
       </c>
       <c r="EA2" t="n">
-        <v>-0.1218367389222659</v>
+        <v>-0.04788386247200054</v>
       </c>
       <c r="EB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC2" t="n">
         <v>-0</v>
@@ -1401,22 +1401,22 @@
         <v>-0</v>
       </c>
       <c r="EE2" t="n">
-        <v>4.280925344400983e-05</v>
+        <v>0.03860442986353995</v>
       </c>
       <c r="EF2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG2" t="n">
-        <v>-0.06985822222488335</v>
+        <v>-0.04840388487657486</v>
       </c>
       <c r="EH2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ2" t="n">
-        <v>0.1133118870862893</v>
+        <v>-0.02933359286308716</v>
       </c>
       <c r="EK2" t="n">
         <v>-0</v>
@@ -1425,97 +1425,97 @@
         <v>-0</v>
       </c>
       <c r="EM2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN2" t="n">
-        <v>0.1639538012860002</v>
+        <v>0.03266384658879508</v>
       </c>
       <c r="EO2" t="n">
         <v>0</v>
       </c>
       <c r="EP2" t="n">
-        <v>-0.0431173721460199</v>
+        <v>-0.03692405290559649</v>
       </c>
       <c r="EQ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER2" t="n">
         <v>-0</v>
       </c>
       <c r="ES2" t="n">
-        <v>-0.07789697510311616</v>
+        <v>0.02626822563803871</v>
       </c>
       <c r="ET2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW2" t="n">
-        <v>0.06794125574655566</v>
+        <v>0.1093844097119162</v>
       </c>
       <c r="EX2" t="n">
         <v>0</v>
       </c>
       <c r="EY2" t="n">
-        <v>-0.1706213772286836</v>
+        <v>-0.1194082902385635</v>
       </c>
       <c r="EZ2" t="n">
         <v>-0</v>
       </c>
       <c r="FA2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB2" t="n">
-        <v>0.00807152775705198</v>
+        <v>0.01148767305031812</v>
       </c>
       <c r="FC2" t="n">
         <v>-0</v>
       </c>
       <c r="FD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF2" t="n">
-        <v>0.08517986307200166</v>
+        <v>0.04722339041255437</v>
       </c>
       <c r="FG2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH2" t="n">
-        <v>0.05951756731383902</v>
+        <v>0.06574527117775006</v>
       </c>
       <c r="FI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK2" t="n">
-        <v>-0.2493124790665496</v>
+        <v>0.02700748135116265</v>
       </c>
       <c r="FL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM2" t="n">
         <v>0</v>
       </c>
       <c r="FN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO2" t="n">
-        <v>-0.006286359179587545</v>
+        <v>0.08596651905567945</v>
       </c>
       <c r="FP2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ2" t="n">
-        <v>-0.04992227918781326</v>
+        <v>-0.009951286004816521</v>
       </c>
       <c r="FR2" t="n">
         <v>-0</v>
@@ -1524,25 +1524,25 @@
         <v>-0</v>
       </c>
       <c r="FT2" t="n">
-        <v>-0.02579917699787081</v>
+        <v>0.006215708230006073</v>
       </c>
       <c r="FU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW2" t="n">
         <v>-0</v>
       </c>
       <c r="FX2" t="n">
-        <v>-0.03625380620550376</v>
+        <v>0.003751388935050632</v>
       </c>
       <c r="FY2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ2" t="n">
-        <v>-0.1852555469648009</v>
+        <v>-0.07943852178054989</v>
       </c>
       <c r="GA2" t="n">
         <v>0</v>
@@ -1551,10 +1551,10 @@
         <v>-0</v>
       </c>
       <c r="GC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE2" t="n">
         <v>-0</v>
@@ -1563,7 +1563,7 @@
         <v>-0</v>
       </c>
       <c r="GG2" t="n">
-        <v>-0.01498923650300059</v>
+        <v>0.01304285789303647</v>
       </c>
     </row>
     <row r="3">
@@ -2706,10 +2706,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.5244371579586645</v>
+        <v>0.0116647827153705</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -2718,13 +2718,13 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.08272772698076998</v>
+        <v>-0.003088136095568473</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1726316916689068</v>
+        <v>-0.002154904353296319</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -2736,7 +2736,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4470171586763059</v>
+        <v>0.02197929643018484</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -2745,13 +2745,13 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0647396292255223</v>
+        <v>-0.006411064174834822</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1907594816959799</v>
+        <v>-0.008476618722729279</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -2763,22 +2763,22 @@
         <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2034763491568378</v>
+        <v>-0.001006507890260457</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2214237063633651</v>
+        <v>-0.008147687755249766</v>
       </c>
       <c r="X5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.04472599369108392</v>
+        <v>0.002083024946705453</v>
       </c>
       <c r="Z5" t="n">
         <v>-0</v>
@@ -2787,52 +2787,52 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.2229371842838425</v>
+        <v>-0.008836214082211823</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.1352255102633211</v>
+        <v>-0.009646915209262261</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.01093808625894644</v>
+        <v>0.001089962927310806</v>
       </c>
       <c r="AI5" t="n">
         <v>-0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.1100184694425895</v>
+        <v>0.0004347091311767136</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.03709101748593414</v>
+        <v>0.0004184496858496599</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.07717723283747634</v>
+        <v>-0.001136344511459555</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -2841,25 +2841,25 @@
         <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.2567907966233577</v>
+        <v>0.008579612604253642</v>
       </c>
       <c r="AV5" t="n">
         <v>-0</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.06593899318816075</v>
+        <v>0.0008446082249784577</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.1189820075010889</v>
+        <v>-0.001066868534566459</v>
       </c>
       <c r="BA5" t="n">
         <v>0</v>
@@ -2871,7 +2871,7 @@
         <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.09604001188342445</v>
+        <v>-0.007809404540764693</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
@@ -2880,40 +2880,40 @@
         <v>0</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.2179637431690206</v>
+        <v>-0.004017776339990837</v>
       </c>
       <c r="BH5" t="n">
         <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.02320624529091621</v>
+        <v>0.003674944413791515</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK5" t="n">
         <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>-0.01301639854557778</v>
+        <v>0.0006065102774290014</v>
       </c>
       <c r="BN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO5" t="n">
         <v>-0</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.1390290174476776</v>
+        <v>0.01387492130635947</v>
       </c>
       <c r="BQ5" t="n">
         <v>-0</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.1354436780249045</v>
+        <v>0.0002258793437818129</v>
       </c>
       <c r="BS5" t="n">
         <v>-0</v>
@@ -2922,25 +2922,25 @@
         <v>-0</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.2956856155088219</v>
+        <v>0.01070421750401473</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.1174685022954683</v>
+        <v>-0.001219532291872415</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
       </c>
       <c r="CA5" t="n">
-        <v>-0.1447066837177511</v>
+        <v>-0.005431009899868612</v>
       </c>
       <c r="CB5" t="n">
         <v>-0</v>
@@ -2949,25 +2949,25 @@
         <v>0</v>
       </c>
       <c r="CD5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.1813104552297142</v>
+        <v>-0.004997596115961862</v>
       </c>
       <c r="CF5" t="n">
         <v>0</v>
       </c>
       <c r="CG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.006840007315629819</v>
+        <v>0.0008086403748666742</v>
       </c>
       <c r="CI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.07368079391113398</v>
+        <v>0.0006584474178910203</v>
       </c>
       <c r="CK5" t="n">
         <v>-0</v>
@@ -2976,25 +2976,25 @@
         <v>-0</v>
       </c>
       <c r="CM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN5" t="n">
-        <v>-0.04533090366907106</v>
+        <v>-0.00396052810442338</v>
       </c>
       <c r="CO5" t="n">
         <v>0</v>
       </c>
       <c r="CP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.1460985891102549</v>
+        <v>-0.00214980952235093</v>
       </c>
       <c r="CR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS5" t="n">
-        <v>-0.03445798606001874</v>
+        <v>-0.003334530669575297</v>
       </c>
       <c r="CT5" t="n">
         <v>0</v>
@@ -3003,10 +3003,10 @@
         <v>-0</v>
       </c>
       <c r="CV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW5" t="n">
-        <v>-0.1658060943846234</v>
+        <v>-0.006613926234681074</v>
       </c>
       <c r="CX5" t="n">
         <v>-0</v>
@@ -3015,13 +3015,13 @@
         <v>0</v>
       </c>
       <c r="CZ5" t="n">
-        <v>-0.02464450407278299</v>
+        <v>0.001031855687884541</v>
       </c>
       <c r="DA5" t="n">
         <v>0</v>
       </c>
       <c r="DB5" t="n">
-        <v>0.1008061429902763</v>
+        <v>0.001602459424453806</v>
       </c>
       <c r="DC5" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="DE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.1358432561367164</v>
+        <v>-0.004217129867689138</v>
       </c>
       <c r="DG5" t="n">
         <v>-0</v>
@@ -3042,13 +3042,13 @@
         <v>0</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.087264635452003</v>
+        <v>-0.01192501508299322</v>
       </c>
       <c r="DJ5" t="n">
         <v>-0</v>
       </c>
       <c r="DK5" t="n">
-        <v>0.01734428282625834</v>
+        <v>-0.000527080284620978</v>
       </c>
       <c r="DL5" t="n">
         <v>-0</v>
@@ -3057,10 +3057,10 @@
         <v>0</v>
       </c>
       <c r="DN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.08042815018531591</v>
+        <v>0.002059865814739327</v>
       </c>
       <c r="DP5" t="n">
         <v>0</v>
@@ -3069,67 +3069,67 @@
         <v>0</v>
       </c>
       <c r="DR5" t="n">
-        <v>-0.1007346162421095</v>
+        <v>0.002734116087916919</v>
       </c>
       <c r="DS5" t="n">
         <v>-0</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.03678403288799686</v>
+        <v>0.006433324274760484</v>
       </c>
       <c r="DU5" t="n">
         <v>-0</v>
       </c>
       <c r="DV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW5" t="n">
         <v>-0</v>
       </c>
       <c r="DX5" t="n">
-        <v>-0.2174344681569411</v>
+        <v>-0.001667124734295496</v>
       </c>
       <c r="DY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ5" t="n">
         <v>-0</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.03646123049128245</v>
+        <v>-0.0003078141516137705</v>
       </c>
       <c r="EB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC5" t="n">
-        <v>0.02451282351213888</v>
+        <v>0.00833847414099371</v>
       </c>
       <c r="ED5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE5" t="n">
         <v>-0</v>
       </c>
       <c r="EF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.08211238961596118</v>
+        <v>-0.007908009073085382</v>
       </c>
       <c r="EH5" t="n">
         <v>0</v>
       </c>
       <c r="EI5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.07216555611140364</v>
+        <v>0.00164100847498162</v>
       </c>
       <c r="EK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL5" t="n">
-        <v>0.1282695714891818</v>
+        <v>-0.004502144493289109</v>
       </c>
       <c r="EM5" t="n">
         <v>-0</v>
@@ -3138,52 +3138,52 @@
         <v>-0</v>
       </c>
       <c r="EO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.1346540576971012</v>
+        <v>-0.00283690026381365</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER5" t="n">
         <v>-0</v>
       </c>
       <c r="ES5" t="n">
-        <v>-0.05375415916580124</v>
+        <v>0.0008411451727996679</v>
       </c>
       <c r="ET5" t="n">
         <v>-0</v>
       </c>
       <c r="EU5" t="n">
-        <v>-0.07601848384453222</v>
+        <v>0.005207667659768355</v>
       </c>
       <c r="EV5" t="n">
         <v>0</v>
       </c>
       <c r="EW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.1691069162963591</v>
+        <v>-0.006935176282250276</v>
       </c>
       <c r="EZ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA5" t="n">
         <v>-0</v>
       </c>
       <c r="FB5" t="n">
-        <v>-0.04070886797367133</v>
+        <v>-0.0005313440144350653</v>
       </c>
       <c r="FC5" t="n">
         <v>-0</v>
       </c>
       <c r="FD5" t="n">
-        <v>0.09985981567048823</v>
+        <v>0.001710687600052184</v>
       </c>
       <c r="FE5" t="n">
         <v>-0</v>
@@ -3192,64 +3192,64 @@
         <v>-0</v>
       </c>
       <c r="FG5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH5" t="n">
-        <v>-0.04509343844617492</v>
+        <v>0.00807589747524916</v>
       </c>
       <c r="FI5" t="n">
         <v>-0</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK5" t="n">
-        <v>-0.04926883998354329</v>
+        <v>0.005473624516792919</v>
       </c>
       <c r="FL5" t="n">
         <v>0</v>
       </c>
       <c r="FM5" t="n">
-        <v>-0.02479457747660654</v>
+        <v>-0.001456127907765254</v>
       </c>
       <c r="FN5" t="n">
         <v>-0</v>
       </c>
       <c r="FO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP5" t="n">
         <v>0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>-0.01893145407038394</v>
+        <v>-0.0003200920258450481</v>
       </c>
       <c r="FR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS5" t="n">
         <v>-0</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.004674958278437745</v>
+        <v>8.59796585874845e-06</v>
       </c>
       <c r="FU5" t="n">
         <v>-0</v>
       </c>
       <c r="FV5" t="n">
-        <v>0.06873382515725933</v>
+        <v>0.009725410584408853</v>
       </c>
       <c r="FW5" t="n">
         <v>-0</v>
       </c>
       <c r="FX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>-0.1520014144245721</v>
+        <v>-0.00684217789354426</v>
       </c>
       <c r="GA5" t="n">
         <v>-0</v>
@@ -3261,16 +3261,16 @@
         <v>0</v>
       </c>
       <c r="GD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE5" t="n">
-        <v>0.003383588796651881</v>
+        <v>0.008537605854552082</v>
       </c>
       <c r="GF5" t="n">
         <v>-0</v>
       </c>
       <c r="GG5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -3847,19 +3847,19 @@
         <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>-1.537115600028207</v>
+        <v>0.4197969174894262</v>
       </c>
       <c r="C7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>1.07798877947071</v>
+        <v>-0.3832937438460396</v>
       </c>
       <c r="E7" t="n">
-        <v>0.07712150213855901</v>
+        <v>0.01473543457863613</v>
       </c>
       <c r="F7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>-0</v>
@@ -3868,49 +3868,49 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.252509774827579</v>
+        <v>0.470293393371461</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9518879571039823</v>
+        <v>-0.4090782345166793</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1418183976532423</v>
+        <v>0.006694463972653337</v>
       </c>
       <c r="O7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>-0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3555832047463938</v>
+        <v>0.1169634922272129</v>
       </c>
       <c r="U7" t="n">
         <v>-0</v>
       </c>
       <c r="V7" t="n">
-        <v>0.1120715770759758</v>
+        <v>-0.03710397408594807</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.09803642053127154</v>
+        <v>-0.02032122832242792</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -3922,22 +3922,22 @@
         <v>-0</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.2499223605218913</v>
+        <v>-0.06939862829061062</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.1735871650396296</v>
+        <v>-0.2222676914631642</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.2316077085713693</v>
+        <v>-0.02695046868431705</v>
       </c>
       <c r="AG7" t="n">
         <v>-0</v>
@@ -3946,28 +3946,28 @@
         <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
         <v>-0</v>
       </c>
       <c r="AL7" t="n">
-        <v>-0.1232582428333826</v>
+        <v>0.1753700936950813</v>
       </c>
       <c r="AM7" t="n">
         <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.2207869734053738</v>
+        <v>-0.08799685876751384</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.1238013972760504</v>
+        <v>0.144827116670552</v>
       </c>
       <c r="AP7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AQ7" t="n">
         <v>0</v>
@@ -3976,58 +3976,58 @@
         <v>0</v>
       </c>
       <c r="AS7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU7" t="n">
-        <v>-0.5395149952277487</v>
+        <v>0.1225059109027951</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.240827310469829</v>
+        <v>-0.1852202416685053</v>
       </c>
       <c r="AX7" t="n">
-        <v>-0.05541788317642208</v>
+        <v>-0.07305097836750393</v>
       </c>
       <c r="AY7" t="n">
         <v>-0</v>
       </c>
       <c r="AZ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA7" t="n">
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
         <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>-0.4099098751823774</v>
+        <v>0.05383039911623374</v>
       </c>
       <c r="BE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.4894536686606486</v>
+        <v>-0.07611017369231898</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.4065846266609614</v>
+        <v>-0.01328566878070709</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
       </c>
       <c r="BI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK7" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="BM7" t="n">
-        <v>-0.1185157928950199</v>
+        <v>-0.1126612017347809</v>
       </c>
       <c r="BN7" t="n">
         <v>0</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.03441993693053259</v>
+        <v>0.06167020431354944</v>
       </c>
       <c r="BP7" t="n">
-        <v>-0.3303331621673907</v>
+        <v>-0.02744676180390072</v>
       </c>
       <c r="BQ7" t="n">
         <v>0</v>
@@ -4054,52 +4054,52 @@
         <v>0</v>
       </c>
       <c r="BS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT7" t="n">
         <v>0</v>
       </c>
       <c r="BU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV7" t="n">
-        <v>-0.7088683235331926</v>
+        <v>0.3144117829249217</v>
       </c>
       <c r="BW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.194613732779274</v>
+        <v>-0.2184290425787161</v>
       </c>
       <c r="BY7" t="n">
-        <v>-0.2255467137230439</v>
+        <v>-0.009561489898462717</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA7" t="n">
         <v>0</v>
       </c>
       <c r="CB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.3657665793802425</v>
+        <v>-0.1833220113542424</v>
       </c>
       <c r="CF7" t="n">
         <v>-0</v>
       </c>
       <c r="CG7" t="n">
-        <v>-0.1940010436453113</v>
+        <v>0.2101281581623029</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.03751190602281729</v>
+        <v>-0.02847153014755955</v>
       </c>
       <c r="CI7" t="n">
         <v>0</v>
@@ -4108,31 +4108,31 @@
         <v>0</v>
       </c>
       <c r="CK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL7" t="n">
         <v>-0</v>
       </c>
       <c r="CM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>-0.03792286571569488</v>
+        <v>-0.1302607333657057</v>
       </c>
       <c r="CO7" t="n">
         <v>-0</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.1606164730296316</v>
+        <v>0.4255307919487149</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.1210653967358087</v>
+        <v>0.1003587706176297</v>
       </c>
       <c r="CR7" t="n">
         <v>-0</v>
       </c>
       <c r="CS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT7" t="n">
         <v>0</v>
@@ -4144,16 +4144,16 @@
         <v>-0</v>
       </c>
       <c r="CW7" t="n">
-        <v>0.3328601575248257</v>
+        <v>-0.1827354348286758</v>
       </c>
       <c r="CX7" t="n">
         <v>0</v>
       </c>
       <c r="CY7" t="n">
-        <v>-0.2780342742928349</v>
+        <v>0.2123215422647773</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.03930280712127598</v>
+        <v>-0.01846247343535696</v>
       </c>
       <c r="DA7" t="n">
         <v>-0</v>
@@ -4162,25 +4162,25 @@
         <v>-0</v>
       </c>
       <c r="DC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.5360206655257143</v>
+        <v>-0.1678502688950475</v>
       </c>
       <c r="DG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH7" t="n">
-        <v>-0.2209952186377437</v>
+        <v>0.0818056753633243</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.1014126223928887</v>
+        <v>-0.1176302046794337</v>
       </c>
       <c r="DJ7" t="n">
         <v>-0</v>
@@ -4189,55 +4189,55 @@
         <v>0</v>
       </c>
       <c r="DL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN7" t="n">
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.07129149697476515</v>
+        <v>-0.06025854252923238</v>
       </c>
       <c r="DP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.02819080083404102</v>
+        <v>0.0895420735852003</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.1744273211990647</v>
+        <v>-0.00140160201518166</v>
       </c>
       <c r="DS7" t="n">
         <v>-0</v>
       </c>
       <c r="DT7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>-0.1339095538776313</v>
+        <v>-0.004627032865274582</v>
       </c>
       <c r="DY7" t="n">
         <v>-0</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.1552872359542127</v>
+        <v>-0.1063026333263819</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.09905427363967528</v>
+        <v>-0.09366799569194707</v>
       </c>
       <c r="EB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC7" t="n">
         <v>-0</v>
@@ -4246,22 +4246,22 @@
         <v>0</v>
       </c>
       <c r="EE7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG7" t="n">
-        <v>0.3048644655833463</v>
+        <v>-0.1584299113173139</v>
       </c>
       <c r="EH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI7" t="n">
-        <v>-0.06759504377861886</v>
+        <v>0.1928022837143886</v>
       </c>
       <c r="EJ7" t="n">
-        <v>-0.2155358595887794</v>
+        <v>0.02304093999178228</v>
       </c>
       <c r="EK7" t="n">
         <v>0</v>
@@ -4273,22 +4273,22 @@
         <v>0</v>
       </c>
       <c r="EN7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP7" t="n">
-        <v>0.139570067885674</v>
+        <v>-0.1554325483413535</v>
       </c>
       <c r="EQ7" t="n">
         <v>-0</v>
       </c>
       <c r="ER7" t="n">
-        <v>-0.2177221919037934</v>
+        <v>0.1222047281451432</v>
       </c>
       <c r="ES7" t="n">
-        <v>-0.0448015491772426</v>
+        <v>0.01536551186290702</v>
       </c>
       <c r="ET7" t="n">
         <v>0</v>
@@ -4297,55 +4297,55 @@
         <v>0</v>
       </c>
       <c r="EV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY7" t="n">
-        <v>0.3452916100382014</v>
+        <v>-0.1976662190494689</v>
       </c>
       <c r="EZ7" t="n">
         <v>-0</v>
       </c>
       <c r="FA7" t="n">
-        <v>-0.231100378677685</v>
+        <v>0.2507310010679774</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.04120023801199523</v>
+        <v>-0.03726998238428898</v>
       </c>
       <c r="FC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD7" t="n">
         <v>0</v>
       </c>
       <c r="FE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF7" t="n">
         <v>-0</v>
       </c>
       <c r="FG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH7" t="n">
-        <v>0.2485073529535438</v>
+        <v>-0.1288298475475162</v>
       </c>
       <c r="FI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ7" t="n">
-        <v>-0.2035715729427133</v>
+        <v>0.1265314270023424</v>
       </c>
       <c r="FK7" t="n">
-        <v>0.03825024257540528</v>
+        <v>0.09499978845811666</v>
       </c>
       <c r="FL7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM7" t="n">
         <v>0</v>
@@ -4357,19 +4357,19 @@
         <v>-0</v>
       </c>
       <c r="FP7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>0.04724292187822824</v>
+        <v>-0.03978225754256919</v>
       </c>
       <c r="FR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS7" t="n">
-        <v>-0.08638384078315524</v>
+        <v>0.1086915621025963</v>
       </c>
       <c r="FT7" t="n">
-        <v>-0.00211423607005114</v>
+        <v>0.01597955634740651</v>
       </c>
       <c r="FU7" t="n">
         <v>0</v>
@@ -4381,54 +4381,54 @@
         <v>-0</v>
       </c>
       <c r="FX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY7" t="n">
         <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>-0.05691010171178437</v>
+        <v>-0.184837570676311</v>
       </c>
       <c r="GA7" t="n">
         <v>0</v>
       </c>
       <c r="GB7" t="n">
-        <v>0.16333405149724</v>
+        <v>0.1917387595248845</v>
       </c>
       <c r="GC7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD7" t="n">
         <v>0</v>
       </c>
       <c r="GE7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF7" t="n">
         <v>-0</v>
       </c>
       <c r="GG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B8" t="n">
-        <v>0.9405697913826785</v>
+        <v>0.5008069522870041</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3163132716763899</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1363657948039965</v>
+        <v>0.09389664377944641</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>-0.4217685434492068</v>
       </c>
       <c r="G8" t="n">
         <v>-0</v>
@@ -4437,31 +4437,31 @@
         <v>-0</v>
       </c>
       <c r="I8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6137760974632578</v>
+        <v>0.5468929025032832</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3832580833800001</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2154841291200038</v>
+        <v>-0.0491406581133419</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>-0.5085745816018247</v>
       </c>
       <c r="P8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -4470,154 +4470,154 @@
         <v>-0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2698226243840993</v>
+        <v>0.04499878992421398</v>
       </c>
       <c r="U8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0483417342412694</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.00305298561546787</v>
+        <v>-0.04569605163356234</v>
       </c>
       <c r="X8" t="n">
-        <v>-0</v>
+        <v>-0.1233841110455355</v>
       </c>
       <c r="Y8" t="n">
         <v>-0</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.2202030416307305</v>
+        <v>0.07694480391154758</v>
       </c>
       <c r="AD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0.007916013172221679</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.02388564414316846</v>
+        <v>-0.2325103584178052</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>0.08240597754643923</v>
       </c>
       <c r="AH8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ8" t="n">
         <v>-0</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.08736385055608605</v>
+        <v>0.1388801275460681</v>
       </c>
       <c r="AM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>-0.09327176770926321</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
-        <v>-0.1322366570640198</v>
+        <v>0.00566293757517644</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>-0.1540760784419851</v>
       </c>
       <c r="AQ8" t="n">
         <v>-0</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS8" t="n">
         <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.6219624380465713</v>
+        <v>0.1952715101845237</v>
       </c>
       <c r="AV8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW8" t="n">
-        <v>-0.0635510589239887</v>
+        <v>-0</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.1472402694186365</v>
+        <v>-0.1123642767123124</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>-0.1933565355770122</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC8" t="n">
         <v>-0</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.1385222727289439</v>
+        <v>0.1323191057785289</v>
       </c>
       <c r="BE8" t="n">
         <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>-0.1698625300406615</v>
+        <v>0</v>
       </c>
       <c r="BG8" t="n">
-        <v>-0.1824795762101906</v>
+        <v>-0.02558001395996499</v>
       </c>
       <c r="BH8" t="n">
-        <v>-0</v>
+        <v>-0.1040450015513013</v>
       </c>
       <c r="BI8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.1747006692014504</v>
+        <v>0.02618779665219876</v>
       </c>
       <c r="BN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.09894979355741738</v>
+        <v>-0</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.3184788868589499</v>
+        <v>0.07819992130814099</v>
       </c>
       <c r="BQ8" t="n">
-        <v>-0</v>
+        <v>0.08383224378643664</v>
       </c>
       <c r="BR8" t="n">
         <v>0</v>
@@ -4626,31 +4626,31 @@
         <v>-0</v>
       </c>
       <c r="BT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.5206775423910329</v>
+        <v>0.3131220062828317</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.002238113957903701</v>
+        <v>0</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.03332793719134448</v>
+        <v>-0.02772742875695252</v>
       </c>
       <c r="BZ8" t="n">
-        <v>-0</v>
+        <v>-0.3527345709041259</v>
       </c>
       <c r="CA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC8" t="n">
         <v>0</v>
@@ -4659,22 +4659,22 @@
         <v>-0</v>
       </c>
       <c r="CE8" t="n">
-        <v>-0.2376574418551704</v>
+        <v>-0.2205709673263539</v>
       </c>
       <c r="CF8" t="n">
         <v>0</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.09446814966921285</v>
+        <v>-0</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.004565381067997424</v>
+        <v>-0.04921276279120928</v>
       </c>
       <c r="CI8" t="n">
-        <v>-0</v>
+        <v>0.2210643083193871</v>
       </c>
       <c r="CJ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK8" t="n">
         <v>0</v>
@@ -4686,25 +4686,25 @@
         <v>0</v>
       </c>
       <c r="CN8" t="n">
-        <v>-0.1355293326006572</v>
+        <v>-0.2644944369341951</v>
       </c>
       <c r="CO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP8" t="n">
-        <v>-0.1978599768003318</v>
+        <v>-0</v>
       </c>
       <c r="CQ8" t="n">
-        <v>-0.3941739526154958</v>
+        <v>0.2383313997379974</v>
       </c>
       <c r="CR8" t="n">
-        <v>0</v>
+        <v>0.2048852869646096</v>
       </c>
       <c r="CS8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU8" t="n">
         <v>0</v>
@@ -4713,25 +4713,25 @@
         <v>0</v>
       </c>
       <c r="CW8" t="n">
-        <v>-0.2198531681919088</v>
+        <v>-0.2024012690478428</v>
       </c>
       <c r="CX8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.1446032978722125</v>
+        <v>0</v>
       </c>
       <c r="CZ8" t="n">
-        <v>-0.03087497614994881</v>
+        <v>-0.02099646480230936</v>
       </c>
       <c r="DA8" t="n">
-        <v>0</v>
+        <v>0.2156598754532523</v>
       </c>
       <c r="DB8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD8" t="n">
         <v>-0</v>
@@ -4740,46 +4740,46 @@
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>-0.2037147091558561</v>
+        <v>-0.2633280019472882</v>
       </c>
       <c r="DG8" t="n">
         <v>0</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.2665903786708507</v>
+        <v>-0</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.01901934226744119</v>
+        <v>-0.3373075129530506</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0</v>
+        <v>0.3658112023774466</v>
       </c>
       <c r="DK8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL8" t="n">
         <v>0</v>
       </c>
       <c r="DM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN8" t="n">
         <v>-0</v>
       </c>
       <c r="DO8" t="n">
-        <v>-0.1391024965788409</v>
+        <v>-0.1014737642319647</v>
       </c>
       <c r="DP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ8" t="n">
-        <v>-0.141530165597752</v>
+        <v>-0</v>
       </c>
       <c r="DR8" t="n">
-        <v>-0.07124603191796332</v>
+        <v>0.01028268523949664</v>
       </c>
       <c r="DS8" t="n">
-        <v>0</v>
+        <v>0.0541017182571729</v>
       </c>
       <c r="DT8" t="n">
         <v>0</v>
@@ -4788,79 +4788,79 @@
         <v>-0</v>
       </c>
       <c r="DV8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.1131470601583329</v>
+        <v>0.007065813021825354</v>
       </c>
       <c r="DY8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ8" t="n">
-        <v>-0.008794274752920441</v>
+        <v>0</v>
       </c>
       <c r="EA8" t="n">
-        <v>-0.1331111197282664</v>
+        <v>0.07107934619569169</v>
       </c>
       <c r="EB8" t="n">
-        <v>0</v>
+        <v>-0.01251030715438</v>
       </c>
       <c r="EC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF8" t="n">
         <v>-0</v>
       </c>
       <c r="EG8" t="n">
-        <v>-0.173471820585896</v>
+        <v>-0.09068077099565448</v>
       </c>
       <c r="EH8" t="n">
         <v>0</v>
       </c>
       <c r="EI8" t="n">
-        <v>-0.2512603278925312</v>
+        <v>-0</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.2140130121457507</v>
+        <v>-0.07639615310194364</v>
       </c>
       <c r="EK8" t="n">
-        <v>0</v>
+        <v>0.1453158232924095</v>
       </c>
       <c r="EL8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN8" t="n">
         <v>-0</v>
       </c>
       <c r="EO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP8" t="n">
-        <v>-0.1278735200170874</v>
+        <v>-0.1669165041284947</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER8" t="n">
-        <v>0.1414019330931688</v>
+        <v>-0</v>
       </c>
       <c r="ES8" t="n">
-        <v>-0.1317023082065069</v>
+        <v>-0.1794146059975145</v>
       </c>
       <c r="ET8" t="n">
-        <v>-0</v>
+        <v>0.1607682125727126</v>
       </c>
       <c r="EU8" t="n">
         <v>-0</v>
@@ -4869,55 +4869,55 @@
         <v>0</v>
       </c>
       <c r="EW8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY8" t="n">
-        <v>-0.2178196426480763</v>
+        <v>-0.2307956842057901</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA8" t="n">
-        <v>0.1334726549126218</v>
+        <v>-0</v>
       </c>
       <c r="FB8" t="n">
-        <v>-0.02328192558486829</v>
+        <v>-0.07653628590665648</v>
       </c>
       <c r="FC8" t="n">
-        <v>-0</v>
+        <v>0.2066818221924365</v>
       </c>
       <c r="FD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH8" t="n">
-        <v>0.01043189736761224</v>
+        <v>-0.2174949391500284</v>
       </c>
       <c r="FI8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0.1163394729111314</v>
+        <v>-0</v>
       </c>
       <c r="FK8" t="n">
-        <v>-0.1072011874187165</v>
+        <v>0.05735355397672191</v>
       </c>
       <c r="FL8" t="n">
-        <v>-0</v>
+        <v>0.2826392163567893</v>
       </c>
       <c r="FM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN8" t="n">
         <v>0</v>
@@ -4926,81 +4926,81 @@
         <v>0</v>
       </c>
       <c r="FP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ8" t="n">
-        <v>0.02903223635890571</v>
+        <v>-0.004003166254628977</v>
       </c>
       <c r="FR8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS8" t="n">
-        <v>-0.006612366092747655</v>
+        <v>-0</v>
       </c>
       <c r="FT8" t="n">
-        <v>-0.1851914939120801</v>
+        <v>0.004969699949585476</v>
       </c>
       <c r="FU8" t="n">
-        <v>-0</v>
+        <v>0.1504514626564303</v>
       </c>
       <c r="FV8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW8" t="n">
         <v>0</v>
       </c>
       <c r="FX8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ8" t="n">
-        <v>-0.07537686919792602</v>
+        <v>-0.06012238744963735</v>
       </c>
       <c r="GA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB8" t="n">
-        <v>-0.01636414408970094</v>
+        <v>-0</v>
       </c>
       <c r="GC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD8" t="n">
-        <v>-0</v>
+        <v>0.1781218397159825</v>
       </c>
       <c r="GE8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>-0.1655384016483287</v>
+        <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3512864081269947</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3737873837179134</v>
+        <v>-0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0556519378991407</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -5009,79 +5009,79 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.09047697229192662</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1721511462828227</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1735874497595981</v>
+        <v>-0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.04817538689925432</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.08284731551748399</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1970953511469149</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.09088388308240564</v>
+        <v>-0</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0.08715209386035551</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.02727319561937367</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>-0</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.08944119540907086</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.03968089460791509</v>
+        <v>-0</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0.04621428222806194</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -5090,79 +5090,79 @@
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>-0.02632215031307424</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AM9" t="n">
-        <v>-0.03039672065499407</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.07114068954335263</v>
+        <v>-0</v>
       </c>
       <c r="AP9" t="n">
         <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.01101059042104026</v>
+        <v>0</v>
       </c>
       <c r="AR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS9" t="n">
         <v>0</v>
       </c>
       <c r="AT9" t="n">
-        <v>-0.03814958628069457</v>
+        <v>0</v>
       </c>
       <c r="AU9" t="n">
         <v>-0</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.2886897386240616</v>
+        <v>0</v>
       </c>
       <c r="AW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.4701312985805261</v>
+        <v>-0</v>
       </c>
       <c r="AY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.02270100169244316</v>
+        <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC9" t="n">
-        <v>-0.09436813610249591</v>
+        <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BE9" t="n">
-        <v>-0.08983711712679805</v>
+        <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.03510119745308692</v>
+        <v>-0</v>
       </c>
       <c r="BH9" t="n">
         <v>0</v>
       </c>
       <c r="BI9" t="n">
-        <v>-0.03961405463328594</v>
+        <v>0</v>
       </c>
       <c r="BJ9" t="n">
         <v>0</v>
@@ -5171,106 +5171,106 @@
         <v>0</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.09995784666753788</v>
+        <v>0</v>
       </c>
       <c r="BM9" t="n">
         <v>-0</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.1975285147513268</v>
+        <v>0</v>
       </c>
       <c r="BO9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.1739327608838931</v>
+        <v>-0</v>
       </c>
       <c r="BQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR9" t="n">
-        <v>-0.0338448233383449</v>
+        <v>0</v>
       </c>
       <c r="BS9" t="n">
         <v>0</v>
       </c>
       <c r="BT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU9" t="n">
-        <v>-0.03593874135238651</v>
+        <v>0</v>
       </c>
       <c r="BV9" t="n">
         <v>-0</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.1641850437923534</v>
+        <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.363494842481543</v>
+        <v>-0</v>
       </c>
       <c r="BZ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.04912253894782304</v>
+        <v>0</v>
       </c>
       <c r="CB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD9" t="n">
-        <v>0.05760728274760893</v>
+        <v>0</v>
       </c>
       <c r="CE9" t="n">
         <v>-0</v>
       </c>
       <c r="CF9" t="n">
-        <v>-0.09947348408711656</v>
+        <v>0</v>
       </c>
       <c r="CG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH9" t="n">
-        <v>-0.04272100128077721</v>
+        <v>-0</v>
       </c>
       <c r="CI9" t="n">
         <v>0</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.01683829940957417</v>
+        <v>0</v>
       </c>
       <c r="CK9" t="n">
         <v>0</v>
       </c>
       <c r="CL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM9" t="n">
-        <v>-0.08782637946434396</v>
+        <v>0</v>
       </c>
       <c r="CN9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CO9" t="n">
-        <v>-0.03820134304149621</v>
+        <v>0</v>
       </c>
       <c r="CP9" t="n">
         <v>0</v>
       </c>
       <c r="CQ9" t="n">
-        <v>-0.2508047242253053</v>
+        <v>-0</v>
       </c>
       <c r="CR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS9" t="n">
-        <v>-0.1116365594774051</v>
+        <v>0</v>
       </c>
       <c r="CT9" t="n">
         <v>0</v>
@@ -5279,106 +5279,106 @@
         <v>0</v>
       </c>
       <c r="CV9" t="n">
-        <v>0.03622274745735254</v>
+        <v>0</v>
       </c>
       <c r="CW9" t="n">
         <v>0</v>
       </c>
       <c r="CX9" t="n">
-        <v>-0.08239532654449713</v>
+        <v>0</v>
       </c>
       <c r="CY9" t="n">
         <v>0</v>
       </c>
       <c r="CZ9" t="n">
-        <v>-0.02741808181815288</v>
+        <v>0</v>
       </c>
       <c r="DA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB9" t="n">
-        <v>0.03931034193327962</v>
+        <v>0</v>
       </c>
       <c r="DC9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD9" t="n">
         <v>0</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.09894868698635909</v>
+        <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DG9" t="n">
-        <v>-0.1514145852433596</v>
+        <v>0</v>
       </c>
       <c r="DH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI9" t="n">
-        <v>-0.04608123877765866</v>
+        <v>-0</v>
       </c>
       <c r="DJ9" t="n">
         <v>0</v>
       </c>
       <c r="DK9" t="n">
-        <v>0.01021164407577824</v>
+        <v>0</v>
       </c>
       <c r="DL9" t="n">
         <v>0</v>
       </c>
       <c r="DM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.03922381153987098</v>
+        <v>0</v>
       </c>
       <c r="DO9" t="n">
         <v>-0</v>
       </c>
       <c r="DP9" t="n">
-        <v>0.03453040939339298</v>
+        <v>0</v>
       </c>
       <c r="DQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR9" t="n">
-        <v>-0.1447165188147784</v>
+        <v>-0</v>
       </c>
       <c r="DS9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.0751020936919919</v>
+        <v>0</v>
       </c>
       <c r="DU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV9" t="n">
         <v>0</v>
       </c>
       <c r="DW9" t="n">
-        <v>-0.05251746999508653</v>
+        <v>0</v>
       </c>
       <c r="DX9" t="n">
         <v>0</v>
       </c>
       <c r="DY9" t="n">
-        <v>0.05832137697627581</v>
+        <v>0</v>
       </c>
       <c r="DZ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA9" t="n">
-        <v>-0.2396144281990006</v>
+        <v>0</v>
       </c>
       <c r="EB9" t="n">
         <v>0</v>
       </c>
       <c r="EC9" t="n">
-        <v>-0.01059854256411494</v>
+        <v>0</v>
       </c>
       <c r="ED9" t="n">
         <v>0</v>
@@ -5387,106 +5387,106 @@
         <v>0</v>
       </c>
       <c r="EF9" t="n">
-        <v>-0.04603659212075518</v>
+        <v>0</v>
       </c>
       <c r="EG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EH9" t="n">
-        <v>-0.2253656983886743</v>
+        <v>0</v>
       </c>
       <c r="EI9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.07025486283094526</v>
+        <v>-0</v>
       </c>
       <c r="EK9" t="n">
         <v>0</v>
       </c>
       <c r="EL9" t="n">
-        <v>-0.01457095535595015</v>
+        <v>0</v>
       </c>
       <c r="EM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO9" t="n">
-        <v>-0.02135007198602744</v>
+        <v>0</v>
       </c>
       <c r="EP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EQ9" t="n">
-        <v>-0.06431865637705522</v>
+        <v>0</v>
       </c>
       <c r="ER9" t="n">
         <v>0</v>
       </c>
       <c r="ES9" t="n">
-        <v>-0.1560830854401518</v>
+        <v>-0</v>
       </c>
       <c r="ET9" t="n">
         <v>0</v>
       </c>
       <c r="EU9" t="n">
-        <v>-0.1153591024528729</v>
+        <v>0</v>
       </c>
       <c r="EV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX9" t="n">
-        <v>0.0270160669710964</v>
+        <v>0</v>
       </c>
       <c r="EY9" t="n">
         <v>-0</v>
       </c>
       <c r="EZ9" t="n">
-        <v>-0.08522478659430779</v>
+        <v>0</v>
       </c>
       <c r="FA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB9" t="n">
-        <v>-0.05664434993403843</v>
+        <v>-0</v>
       </c>
       <c r="FC9" t="n">
         <v>0</v>
       </c>
       <c r="FD9" t="n">
-        <v>0.01782375133092097</v>
+        <v>0</v>
       </c>
       <c r="FE9" t="n">
         <v>0</v>
       </c>
       <c r="FF9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG9" t="n">
-        <v>0.1310609150217981</v>
+        <v>0</v>
       </c>
       <c r="FH9" t="n">
         <v>-0</v>
       </c>
       <c r="FI9" t="n">
-        <v>0.02718398736281518</v>
+        <v>0</v>
       </c>
       <c r="FJ9" t="n">
         <v>0</v>
       </c>
       <c r="FK9" t="n">
-        <v>-0.06640549877895308</v>
+        <v>-0</v>
       </c>
       <c r="FL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM9" t="n">
-        <v>-0.08734512236424488</v>
+        <v>0</v>
       </c>
       <c r="FN9" t="n">
         <v>0</v>
@@ -5495,25 +5495,25 @@
         <v>0</v>
       </c>
       <c r="FP9" t="n">
-        <v>0.05792824663696166</v>
+        <v>0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FR9" t="n">
-        <v>0.09332216229887522</v>
+        <v>0</v>
       </c>
       <c r="FS9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FT9" t="n">
-        <v>-0.02085137404521642</v>
+        <v>-0</v>
       </c>
       <c r="FU9" t="n">
         <v>0</v>
       </c>
       <c r="FV9" t="n">
-        <v>-0.1220199769713756</v>
+        <v>0</v>
       </c>
       <c r="FW9" t="n">
         <v>0</v>
@@ -5522,28 +5522,28 @@
         <v>0</v>
       </c>
       <c r="FY9" t="n">
-        <v>-0.08689990484916404</v>
+        <v>0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GA9" t="n">
-        <v>0.04685319587733858</v>
+        <v>0</v>
       </c>
       <c r="GB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GC9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE9" t="n">
-        <v>-0.03202472895915883</v>
+        <v>0</v>
       </c>
       <c r="GF9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG9" t="n">
         <v>0</v>
@@ -5551,82 +5551,82 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>-1.01523555821666</v>
+        <v>0.06931929943717148</v>
       </c>
       <c r="C10" t="n">
         <v>-0</v>
       </c>
       <c r="D10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0.09600098812621007</v>
+        <v>0.01706901304945652</v>
       </c>
       <c r="F10" t="n">
-        <v>1.299257065952552</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>-0.05886228878668291</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J10" t="n">
         <v>-0</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.616036509686948</v>
+        <v>0.07278597965268337</v>
       </c>
       <c r="L10" t="n">
         <v>-0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0.03269780431030718</v>
+        <v>-0.05034419435558576</v>
       </c>
       <c r="O10" t="n">
-        <v>0.8793423788601684</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-0.1142234181289752</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1088552068665907</v>
+        <v>0.07915591308807648</v>
       </c>
       <c r="U10" t="n">
         <v>-0</v>
       </c>
       <c r="V10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1605689715810021</v>
+        <v>-0.02546448388553789</v>
       </c>
       <c r="X10" t="n">
-        <v>0.2444548282141922</v>
+        <v>-0</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>-0</v>
+        <v>-0.05384368111613623</v>
       </c>
       <c r="AA10" t="n">
         <v>-0</v>
@@ -5635,187 +5635,187 @@
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>-0.1243585485744076</v>
+        <v>-0.05361812208468392</v>
       </c>
       <c r="AD10" t="n">
         <v>-0</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.001139860921079179</v>
+        <v>-0.09064913223393507</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.02749102796114439</v>
+        <v>-0</v>
       </c>
       <c r="AH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>-0</v>
+        <v>0.06851300436837439</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK10" t="n">
         <v>-0</v>
       </c>
       <c r="AL10" t="n">
-        <v>-0.1282016144597799</v>
+        <v>0.071248781797789</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.1466013198481134</v>
+        <v>0.04013492066618559</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.3467680070393685</v>
+        <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>0.03946720597392436</v>
       </c>
       <c r="AS10" t="n">
         <v>-0</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU10" t="n">
-        <v>-0.4455803754393465</v>
+        <v>0.0440594012713064</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW10" t="n">
         <v>-0</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.1393397121788306</v>
+        <v>-0.006512189688678427</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.7463091732373981</v>
+        <v>0</v>
       </c>
       <c r="AZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>-0.004180863264492946</v>
       </c>
       <c r="BB10" t="n">
         <v>-0</v>
       </c>
       <c r="BC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>-0.4110492844057702</v>
+        <v>-0.04013413008262309</v>
       </c>
       <c r="BE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.122583505464526</v>
+        <v>-0.1511531474938312</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.2556691308527019</v>
+        <v>0</v>
       </c>
       <c r="BI10" t="n">
         <v>0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>-0</v>
+        <v>-0.04315535571455806</v>
       </c>
       <c r="BK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM10" t="n">
-        <v>-0.3061581257089731</v>
+        <v>0.0347599692921372</v>
       </c>
       <c r="BN10" t="n">
         <v>-0</v>
       </c>
       <c r="BO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP10" t="n">
-        <v>-0.1433122467154546</v>
+        <v>0.06881996438145854</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.1447537175027178</v>
+        <v>-0</v>
       </c>
       <c r="BR10" t="n">
         <v>0</v>
       </c>
       <c r="BS10" t="n">
-        <v>-0</v>
+        <v>0.01163185686508543</v>
       </c>
       <c r="BT10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV10" t="n">
-        <v>-0.4711882662228642</v>
+        <v>0.1327550092965236</v>
       </c>
       <c r="BW10" t="n">
         <v>-0</v>
       </c>
       <c r="BX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.1672099941345414</v>
+        <v>0.04736416975574528</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.5590962446661237</v>
+        <v>0</v>
       </c>
       <c r="CA10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB10" t="n">
-        <v>0</v>
+        <v>-0.05804949555259091</v>
       </c>
       <c r="CC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD10" t="n">
         <v>-0</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.2593563236097431</v>
+        <v>-0.02431910788714689</v>
       </c>
       <c r="CF10" t="n">
         <v>-0</v>
       </c>
       <c r="CG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH10" t="n">
-        <v>-0.01428612902392847</v>
+        <v>-0.01054444664228794</v>
       </c>
       <c r="CI10" t="n">
-        <v>-0.2706546286537403</v>
+        <v>-0</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK10" t="n">
-        <v>-0</v>
+        <v>0.01762804440108104</v>
       </c>
       <c r="CL10" t="n">
         <v>-0</v>
@@ -5824,34 +5824,34 @@
         <v>-0</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.1167886623678485</v>
+        <v>-0.05775591040285852</v>
       </c>
       <c r="CO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP10" t="n">
         <v>0</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-0.2586802439507907</v>
+        <v>0.1375231725256544</v>
       </c>
       <c r="CR10" t="n">
-        <v>-0.06308999645817082</v>
+        <v>-0</v>
       </c>
       <c r="CS10" t="n">
         <v>-0</v>
       </c>
       <c r="CT10" t="n">
-        <v>0</v>
+        <v>0.05553479053228475</v>
       </c>
       <c r="CU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV10" t="n">
         <v>0</v>
       </c>
       <c r="CW10" t="n">
-        <v>0.2193058003689634</v>
+        <v>-0.02021101588114087</v>
       </c>
       <c r="CX10" t="n">
         <v>0</v>
@@ -5860,25 +5860,25 @@
         <v>-0</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.00613885897459405</v>
+        <v>-0.006873768020088342</v>
       </c>
       <c r="DA10" t="n">
-        <v>-0.2527945286530076</v>
+        <v>0</v>
       </c>
       <c r="DB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC10" t="n">
-        <v>0</v>
+        <v>0.03609712989819813</v>
       </c>
       <c r="DD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE10" t="n">
         <v>-0</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.05304711002146733</v>
+        <v>-0.09426503085681393</v>
       </c>
       <c r="DG10" t="n">
         <v>0</v>
@@ -5887,16 +5887,16 @@
         <v>0</v>
       </c>
       <c r="DI10" t="n">
-        <v>-0.05592949615329957</v>
+        <v>0.02397029361923552</v>
       </c>
       <c r="DJ10" t="n">
-        <v>-0.2231255039826979</v>
+        <v>0</v>
       </c>
       <c r="DK10" t="n">
         <v>-0</v>
       </c>
       <c r="DL10" t="n">
-        <v>-0</v>
+        <v>-0.02503776447284571</v>
       </c>
       <c r="DM10" t="n">
         <v>-0</v>
@@ -5905,25 +5905,25 @@
         <v>-0</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.02378144885933687</v>
+        <v>-0.02650349863723559</v>
       </c>
       <c r="DP10" t="n">
         <v>-0</v>
       </c>
       <c r="DQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR10" t="n">
-        <v>-0.01561074395181454</v>
+        <v>-0.03633181774265338</v>
       </c>
       <c r="DS10" t="n">
-        <v>-0.0544358518979103</v>
+        <v>-0</v>
       </c>
       <c r="DT10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU10" t="n">
-        <v>0</v>
+        <v>-0.02081394308503982</v>
       </c>
       <c r="DV10" t="n">
         <v>0</v>
@@ -5932,25 +5932,25 @@
         <v>-0</v>
       </c>
       <c r="DX10" t="n">
-        <v>-0.1855612845181854</v>
+        <v>0.04166213624377171</v>
       </c>
       <c r="DY10" t="n">
         <v>0</v>
       </c>
       <c r="DZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.235300067208479</v>
+        <v>-0.05891345785117798</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.01458149206158613</v>
+        <v>-0</v>
       </c>
       <c r="EC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED10" t="n">
-        <v>-0</v>
+        <v>-0.02174416646068146</v>
       </c>
       <c r="EE10" t="n">
         <v>-0</v>
@@ -5959,25 +5959,25 @@
         <v>-0</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.2128005970763474</v>
+        <v>0.01573929826367676</v>
       </c>
       <c r="EH10" t="n">
         <v>-0</v>
       </c>
       <c r="EI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ10" t="n">
-        <v>-0.1112603022993998</v>
+        <v>-0.06627492969893149</v>
       </c>
       <c r="EK10" t="n">
-        <v>-0.08666489394692195</v>
+        <v>-0</v>
       </c>
       <c r="EL10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM10" t="n">
-        <v>-0</v>
+        <v>0.02586756925510457</v>
       </c>
       <c r="EN10" t="n">
         <v>0</v>
@@ -5986,25 +5986,25 @@
         <v>-0</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.1253008193523145</v>
+        <v>-0.0222379402561288</v>
       </c>
       <c r="EQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER10" t="n">
         <v>0</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.01451137328821416</v>
+        <v>-0.04632945356604269</v>
       </c>
       <c r="ET10" t="n">
-        <v>-0.164421773862654</v>
+        <v>0</v>
       </c>
       <c r="EU10" t="n">
         <v>0</v>
       </c>
       <c r="EV10" t="n">
-        <v>-0</v>
+        <v>0.06145765543758978</v>
       </c>
       <c r="EW10" t="n">
         <v>-0</v>
@@ -6013,7 +6013,7 @@
         <v>-0</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.226352501574621</v>
+        <v>-0.02272817348304748</v>
       </c>
       <c r="EZ10" t="n">
         <v>-0</v>
@@ -6022,70 +6022,70 @@
         <v>0</v>
       </c>
       <c r="FB10" t="n">
-        <v>-0.04854111526301848</v>
+        <v>-0.0245696653594833</v>
       </c>
       <c r="FC10" t="n">
-        <v>-0.2441666613946729</v>
+        <v>-0</v>
       </c>
       <c r="FD10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE10" t="n">
-        <v>-0</v>
+        <v>0.04663026247169673</v>
       </c>
       <c r="FF10" t="n">
         <v>-0</v>
       </c>
       <c r="FG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.07523824653763106</v>
+        <v>0.01941214688152859</v>
       </c>
       <c r="FI10" t="n">
         <v>-0</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.2026650530480686</v>
+        <v>0.05073067109999425</v>
       </c>
       <c r="FL10" t="n">
-        <v>-0.3293955369473157</v>
+        <v>-0</v>
       </c>
       <c r="FM10" t="n">
         <v>0</v>
       </c>
       <c r="FN10" t="n">
-        <v>0</v>
+        <v>-0.02323956037500877</v>
       </c>
       <c r="FO10" t="n">
         <v>-0</v>
       </c>
       <c r="FP10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.03367309845101453</v>
+        <v>0.002631781569309517</v>
       </c>
       <c r="FR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS10" t="n">
         <v>0</v>
       </c>
       <c r="FT10" t="n">
-        <v>-0.1410445907916998</v>
+        <v>0.0141243250300953</v>
       </c>
       <c r="FU10" t="n">
-        <v>0.007780699965548411</v>
+        <v>0</v>
       </c>
       <c r="FV10" t="n">
         <v>0</v>
       </c>
       <c r="FW10" t="n">
-        <v>-0</v>
+        <v>0.02974929024638967</v>
       </c>
       <c r="FX10" t="n">
         <v>-0</v>
@@ -6094,48 +6094,48 @@
         <v>0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.05363257659120307</v>
+        <v>-0.05356039373028217</v>
       </c>
       <c r="GA10" t="n">
         <v>0</v>
       </c>
       <c r="GB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC10" t="n">
         <v>-0</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.1706947374222852</v>
+        <v>0</v>
       </c>
       <c r="GE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF10" t="n">
-        <v>-0</v>
+        <v>0.02709608005393344</v>
       </c>
       <c r="GG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0</v>
+        <v>0.3689631904156975</v>
       </c>
       <c r="B11" t="n">
-        <v>0.1364446040764817</v>
+        <v>-0.7966695428757107</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.01529134798576143</v>
+        <v>0.2525091949038147</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.07891539885748054</v>
+        <v>-0</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -6144,82 +6144,82 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>0.278147175962463</v>
       </c>
       <c r="K11" t="n">
-        <v>0.09015323897684376</v>
+        <v>-0.9007729175679317</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0267125732675682</v>
+        <v>0.3189493685754606</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.07548151299726595</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R11" t="n">
         <v>-0</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>-0.09364818373223649</v>
       </c>
       <c r="T11" t="n">
-        <v>0.02248529879997976</v>
+        <v>-0.0479964093868543</v>
       </c>
       <c r="U11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.005789584403809348</v>
+        <v>0.01634461924117507</v>
       </c>
       <c r="X11" t="n">
-        <v>0.01287595108783647</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB11" t="n">
-        <v>-0</v>
+        <v>0.2314061515546157</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.01762029509310406</v>
+        <v>0.04166642311673993</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE11" t="n">
         <v>-0</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.01027705501743932</v>
+        <v>0.1589798234565496</v>
       </c>
       <c r="AG11" t="n">
-        <v>-0.006396756038661381</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -6228,49 +6228,49 @@
         <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>0.04639324175931037</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.003888808952701278</v>
+        <v>-0.2869568350377955</v>
       </c>
       <c r="AM11" t="n">
         <v>-0</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO11" t="n">
-        <v>-0.02682946508539239</v>
+        <v>0.0606464107884858</v>
       </c>
       <c r="AP11" t="n">
-        <v>-0.01728883620600441</v>
+        <v>-0</v>
       </c>
       <c r="AQ11" t="n">
         <v>0</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT11" t="n">
-        <v>-0</v>
+        <v>0.02574945312627294</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.07059543046792759</v>
+        <v>-0.3210268916097038</v>
       </c>
       <c r="AV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW11" t="n">
         <v>-0</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.0003570618753894992</v>
+        <v>0.0404058614479326</v>
       </c>
       <c r="AY11" t="n">
-        <v>-0.01301994159694863</v>
+        <v>0</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
@@ -6279,28 +6279,28 @@
         <v>-0</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>0.2231873183017805</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.04853347725056242</v>
+        <v>-0.1306748619231554</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG11" t="n">
-        <v>-0.04457993870232572</v>
+        <v>0.1791049856937381</v>
       </c>
       <c r="BH11" t="n">
-        <v>-0.05921805229505812</v>
+        <v>-0</v>
       </c>
       <c r="BI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ11" t="n">
         <v>0</v>
@@ -6309,52 +6309,52 @@
         <v>-0</v>
       </c>
       <c r="BL11" t="n">
-        <v>-0</v>
+        <v>-0.07862813611245376</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.05904950255337194</v>
+        <v>-0.1665268720464136</v>
       </c>
       <c r="BN11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.04326045893188176</v>
+        <v>-0.1980730302931266</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.01002423074745777</v>
+        <v>0</v>
       </c>
       <c r="BR11" t="n">
         <v>-0</v>
       </c>
       <c r="BS11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT11" t="n">
         <v>0</v>
       </c>
       <c r="BU11" t="n">
-        <v>-0</v>
+        <v>-0.09596045485984317</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.04904855986525251</v>
+        <v>-0.5044795501745137</v>
       </c>
       <c r="BW11" t="n">
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.008881170629790117</v>
+        <v>0.06948186262225672</v>
       </c>
       <c r="BZ11" t="n">
-        <v>-0.004319706383300165</v>
+        <v>-0</v>
       </c>
       <c r="CA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB11" t="n">
         <v>-0</v>
@@ -6363,10 +6363,10 @@
         <v>-0</v>
       </c>
       <c r="CD11" t="n">
-        <v>-0</v>
+        <v>-0.1585428514542155</v>
       </c>
       <c r="CE11" t="n">
-        <v>-0.02743307525126803</v>
+        <v>0.3102266039067982</v>
       </c>
       <c r="CF11" t="n">
         <v>0</v>
@@ -6375,37 +6375,37 @@
         <v>0</v>
       </c>
       <c r="CH11" t="n">
-        <v>-0.001718727309518959</v>
+        <v>-0.0287569988300447</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.02464327366427905</v>
+        <v>0</v>
       </c>
       <c r="CJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL11" t="n">
         <v>0</v>
       </c>
       <c r="CM11" t="n">
-        <v>0</v>
+        <v>0.04204210445187586</v>
       </c>
       <c r="CN11" t="n">
-        <v>-0.02832040283563373</v>
+        <v>0.5759872374244062</v>
       </c>
       <c r="CO11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP11" t="n">
         <v>0</v>
       </c>
       <c r="CQ11" t="n">
-        <v>0.002243613834086771</v>
+        <v>0.03755042673462831</v>
       </c>
       <c r="CR11" t="n">
-        <v>-0.007253974229492828</v>
+        <v>0</v>
       </c>
       <c r="CS11" t="n">
         <v>0</v>
@@ -6417,37 +6417,37 @@
         <v>0</v>
       </c>
       <c r="CV11" t="n">
-        <v>-0</v>
+        <v>-0.1291602850954395</v>
       </c>
       <c r="CW11" t="n">
-        <v>-0.01744193599216252</v>
+        <v>0.3133981183805227</v>
       </c>
       <c r="CX11" t="n">
         <v>-0</v>
       </c>
       <c r="CY11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ11" t="n">
-        <v>-0.0007379786198055919</v>
+        <v>-0.01239027895954505</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.0235687538478754</v>
+        <v>-0</v>
       </c>
       <c r="DB11" t="n">
         <v>0</v>
       </c>
       <c r="DC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE11" t="n">
-        <v>-0</v>
+        <v>-0.08096824120840518</v>
       </c>
       <c r="DF11" t="n">
-        <v>-0.03934244765089095</v>
+        <v>0.3859790224954018</v>
       </c>
       <c r="DG11" t="n">
         <v>0</v>
@@ -6456,10 +6456,10 @@
         <v>-0</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.01096392675926109</v>
+        <v>0.1253371114193522</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.00243560789658034</v>
+        <v>0</v>
       </c>
       <c r="DK11" t="n">
         <v>0</v>
@@ -6468,55 +6468,55 @@
         <v>-0</v>
       </c>
       <c r="DM11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN11" t="n">
-        <v>-0</v>
+        <v>0.08981652405436942</v>
       </c>
       <c r="DO11" t="n">
-        <v>-0.02810403422185292</v>
+        <v>0.1863301896031568</v>
       </c>
       <c r="DP11" t="n">
         <v>0</v>
       </c>
       <c r="DQ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.007584270899308072</v>
+        <v>0.03447830609701267</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.008091523767714097</v>
+        <v>-0</v>
       </c>
       <c r="DT11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW11" t="n">
-        <v>-0</v>
+        <v>-0.1926000625635877</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.01420265420713893</v>
+        <v>-0.06796676540027696</v>
       </c>
       <c r="DY11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ11" t="n">
         <v>-0</v>
       </c>
       <c r="EA11" t="n">
-        <v>-0.0124929642671575</v>
+        <v>-0.07041371869357525</v>
       </c>
       <c r="EB11" t="n">
-        <v>-0.01833291033144892</v>
+        <v>0</v>
       </c>
       <c r="EC11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED11" t="n">
         <v>-0</v>
@@ -6525,10 +6525,10 @@
         <v>0</v>
       </c>
       <c r="EF11" t="n">
-        <v>-0</v>
+        <v>-0.06814198411674256</v>
       </c>
       <c r="EG11" t="n">
-        <v>-0.004388975209772096</v>
+        <v>0.1996599137848367</v>
       </c>
       <c r="EH11" t="n">
         <v>-0</v>
@@ -6537,52 +6537,52 @@
         <v>0</v>
       </c>
       <c r="EJ11" t="n">
-        <v>-0.005195997755256241</v>
+        <v>0.05325442275169104</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.01137870883508485</v>
+        <v>0</v>
       </c>
       <c r="EL11" t="n">
         <v>-0</v>
       </c>
       <c r="EM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN11" t="n">
         <v>0</v>
       </c>
       <c r="EO11" t="n">
-        <v>0</v>
+        <v>-0.01217838306674554</v>
       </c>
       <c r="EP11" t="n">
-        <v>-0.002115757764273628</v>
+        <v>0.2226159029996326</v>
       </c>
       <c r="EQ11" t="n">
         <v>-0</v>
       </c>
       <c r="ER11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES11" t="n">
-        <v>0.01274236019734721</v>
+        <v>0.02128867792323171</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.01080174327539466</v>
+        <v>0</v>
       </c>
       <c r="EU11" t="n">
         <v>0</v>
       </c>
       <c r="EV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX11" t="n">
-        <v>-0</v>
+        <v>-0.1545491366202259</v>
       </c>
       <c r="EY11" t="n">
-        <v>-0.0179384743515631</v>
+        <v>0.3792245807485697</v>
       </c>
       <c r="EZ11" t="n">
         <v>0</v>
@@ -6591,97 +6591,97 @@
         <v>0</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.001568873949862859</v>
+        <v>0.0127200519525501</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.02795226844038717</v>
+        <v>0</v>
       </c>
       <c r="FD11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF11" t="n">
         <v>0</v>
       </c>
       <c r="FG11" t="n">
-        <v>0</v>
+        <v>-0.04937678347684814</v>
       </c>
       <c r="FH11" t="n">
-        <v>-0.003128781657310411</v>
+        <v>0.1493407620560619</v>
       </c>
       <c r="FI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ11" t="n">
         <v>0</v>
       </c>
       <c r="FK11" t="n">
-        <v>-0.0275154466131817</v>
+        <v>-0.1396495845453288</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.01971626590765714</v>
+        <v>-0</v>
       </c>
       <c r="FM11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO11" t="n">
         <v>0</v>
       </c>
       <c r="FP11" t="n">
-        <v>-0</v>
+        <v>0.1001675641779822</v>
       </c>
       <c r="FQ11" t="n">
-        <v>-8.404413649073535e-05</v>
+        <v>-0.007136058439131253</v>
       </c>
       <c r="FR11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FT11" t="n">
-        <v>-0.00182443683939502</v>
+        <v>-0.05245208588438422</v>
       </c>
       <c r="FU11" t="n">
-        <v>0.02057096350365135</v>
+        <v>0</v>
       </c>
       <c r="FV11" t="n">
         <v>-0</v>
       </c>
       <c r="FW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY11" t="n">
-        <v>-0</v>
+        <v>-0.1365709581004295</v>
       </c>
       <c r="FZ11" t="n">
-        <v>-0.02985760876822176</v>
+        <v>0.2509049263357963</v>
       </c>
       <c r="GA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD11" t="n">
-        <v>-0.01407970167790943</v>
+        <v>-0</v>
       </c>
       <c r="GE11" t="n">
         <v>0</v>
       </c>
       <c r="GF11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG11" t="n">
         <v>-0</v>
@@ -6692,106 +6692,106 @@
         <v>-0</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.2965027281243298</v>
+        <v>0.382947643268892</v>
       </c>
       <c r="C12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2049275554189547</v>
+        <v>-0.2161824498826097</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2130994498817284</v>
+        <v>-0.07397305175414848</v>
       </c>
       <c r="F12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>-0</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.1814740539325028</v>
+        <v>0.371869690722985</v>
       </c>
       <c r="L12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1482927035423456</v>
+        <v>-0.3077346916187941</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1634607949514152</v>
+        <v>-0.1688141921760581</v>
       </c>
       <c r="O12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>-0</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.09488741912369433</v>
+        <v>0.0725037607706582</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>0.03245697209241411</v>
+        <v>0.0004113071460205886</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.003948715531136015</v>
+        <v>0.02692340991284889</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z12" t="n">
         <v>-0</v>
       </c>
       <c r="AA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
         <v>-0</v>
       </c>
       <c r="AC12" t="n">
-        <v>-0.0674932280097869</v>
+        <v>3.305559106559331e-05</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0.01508751037809647</v>
+        <v>-0.05560732560712298</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.01695634159859969</v>
+        <v>-0.108227056549687</v>
       </c>
       <c r="AG12" t="n">
         <v>-0</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
         <v>0</v>
@@ -6800,19 +6800,19 @@
         <v>-0</v>
       </c>
       <c r="AL12" t="n">
-        <v>-0.05155254189306302</v>
+        <v>0.1280314571716156</v>
       </c>
       <c r="AM12" t="n">
         <v>-0</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.03371337399170132</v>
+        <v>-0.08548140457380536</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.06645992452428311</v>
+        <v>0.09143000506537102</v>
       </c>
       <c r="AP12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AQ12" t="n">
         <v>0</v>
@@ -6821,85 +6821,85 @@
         <v>-0</v>
       </c>
       <c r="AS12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT12" t="n">
         <v>-0</v>
       </c>
       <c r="AU12" t="n">
-        <v>-0.1773207088767321</v>
+        <v>0.2729102478511394</v>
       </c>
       <c r="AV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.01245354643042772</v>
+        <v>-0.07455767025524804</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.03808187437787838</v>
+        <v>-0.04453155328684261</v>
       </c>
       <c r="AY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC12" t="n">
         <v>-0</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.01750367116651472</v>
+        <v>-0.09419152112452507</v>
       </c>
       <c r="BE12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>0.1001427922899764</v>
+        <v>0.0376610648808611</v>
       </c>
       <c r="BG12" t="n">
-        <v>0.2228027112098224</v>
+        <v>-0.004630710933295529</v>
       </c>
       <c r="BH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BI12" t="n">
         <v>0</v>
       </c>
       <c r="BJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL12" t="n">
         <v>0</v>
       </c>
       <c r="BM12" t="n">
-        <v>-0.02868967240327079</v>
+        <v>-0.03625306109683345</v>
       </c>
       <c r="BN12" t="n">
         <v>0</v>
       </c>
       <c r="BO12" t="n">
-        <v>-0.02984537668348191</v>
+        <v>0.05351754137473696</v>
       </c>
       <c r="BP12" t="n">
-        <v>-0.0722994869440369</v>
+        <v>0.1105699606124965</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BR12" t="n">
         <v>0</v>
       </c>
       <c r="BS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT12" t="n">
         <v>0</v>
@@ -6908,52 +6908,52 @@
         <v>-0</v>
       </c>
       <c r="BV12" t="n">
-        <v>-0.1673396709240404</v>
+        <v>0.2921078382907668</v>
       </c>
       <c r="BW12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>-0.0140924407815481</v>
+        <v>-0.226252747747476</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.05168596250973371</v>
+        <v>0.04527625780413421</v>
       </c>
       <c r="BZ12" t="n">
         <v>0</v>
       </c>
       <c r="CA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC12" t="n">
         <v>0</v>
       </c>
       <c r="CD12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE12" t="n">
-        <v>0.0755223184463109</v>
+        <v>-0.1092753199894443</v>
       </c>
       <c r="CF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG12" t="n">
-        <v>-0.02015756583461784</v>
+        <v>0.1217066882950505</v>
       </c>
       <c r="CH12" t="n">
-        <v>-0.004565152909887009</v>
+        <v>0.02071646596940983</v>
       </c>
       <c r="CI12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ12" t="n">
         <v>0</v>
       </c>
       <c r="CK12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL12" t="n">
         <v>-0</v>
@@ -6962,46 +6962,46 @@
         <v>-0</v>
       </c>
       <c r="CN12" t="n">
-        <v>-0.04177490260689569</v>
+        <v>-0.09961051100034347</v>
       </c>
       <c r="CO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP12" t="n">
-        <v>0.05742813548262718</v>
+        <v>0.1162313080565425</v>
       </c>
       <c r="CQ12" t="n">
-        <v>0.06248366578190469</v>
+        <v>-0.06916930323307835</v>
       </c>
       <c r="CR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU12" t="n">
         <v>-0</v>
       </c>
       <c r="CV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW12" t="n">
-        <v>0.06260855365499753</v>
+        <v>-0.1127145564772687</v>
       </c>
       <c r="CX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY12" t="n">
-        <v>-0.03218220713967085</v>
+        <v>0.1279683231509281</v>
       </c>
       <c r="CZ12" t="n">
-        <v>-0.002059616650143921</v>
+        <v>0.03711727600556042</v>
       </c>
       <c r="DA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB12" t="n">
         <v>-0</v>
@@ -7010,85 +7010,85 @@
         <v>0</v>
       </c>
       <c r="DD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.04680996420915204</v>
+        <v>-0.06065638510179607</v>
       </c>
       <c r="DG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH12" t="n">
-        <v>-0.02811673504434668</v>
+        <v>0.03482374293208432</v>
       </c>
       <c r="DI12" t="n">
-        <v>-0.003592145609605059</v>
+        <v>-0.1246176629013736</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK12" t="n">
         <v>0</v>
       </c>
       <c r="DL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM12" t="n">
         <v>-0</v>
       </c>
       <c r="DN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO12" t="n">
-        <v>0.04389358778046593</v>
+        <v>0.07855778434540488</v>
       </c>
       <c r="DP12" t="n">
         <v>0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.005078070230876293</v>
+        <v>0.01550119086987716</v>
       </c>
       <c r="DR12" t="n">
-        <v>0.03880354324643522</v>
+        <v>-0.0612467774070375</v>
       </c>
       <c r="DS12" t="n">
         <v>-0</v>
       </c>
       <c r="DT12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.005274042568141197</v>
+        <v>-0.03966941708480811</v>
       </c>
       <c r="DY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ12" t="n">
-        <v>0.01130474229121535</v>
+        <v>0.04007444914549508</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.04223621111896739</v>
+        <v>-0.04484454009395469</v>
       </c>
       <c r="EB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC12" t="n">
         <v>0</v>
       </c>
       <c r="ED12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE12" t="n">
         <v>-0</v>
@@ -7097,79 +7097,79 @@
         <v>-0</v>
       </c>
       <c r="EG12" t="n">
-        <v>0.03701106434439249</v>
+        <v>-0.0653358783792324</v>
       </c>
       <c r="EH12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI12" t="n">
-        <v>-0.02174006316197236</v>
+        <v>0.09168129118960958</v>
       </c>
       <c r="EJ12" t="n">
-        <v>-0.06892157530729141</v>
+        <v>0.04283345193421272</v>
       </c>
       <c r="EK12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL12" t="n">
         <v>0</v>
       </c>
       <c r="EM12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO12" t="n">
         <v>-0</v>
       </c>
       <c r="EP12" t="n">
-        <v>0.02596724294509193</v>
+        <v>0.009178491991187206</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER12" t="n">
-        <v>-0.009689348308374987</v>
+        <v>-0.1171054953046298</v>
       </c>
       <c r="ES12" t="n">
-        <v>-0.002347311336146895</v>
+        <v>-0.06843930233543975</v>
       </c>
       <c r="ET12" t="n">
         <v>0</v>
       </c>
       <c r="EU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY12" t="n">
-        <v>0.05730590501542911</v>
+        <v>-0.1249219288217432</v>
       </c>
       <c r="EZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA12" t="n">
-        <v>-0.02995919560177928</v>
+        <v>0.1221362371982818</v>
       </c>
       <c r="FB12" t="n">
-        <v>-0.00756671920183698</v>
+        <v>0.0003734373889710202</v>
       </c>
       <c r="FC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD12" t="n">
         <v>0</v>
       </c>
       <c r="FE12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF12" t="n">
         <v>-0</v>
@@ -7178,16 +7178,16 @@
         <v>-0</v>
       </c>
       <c r="FH12" t="n">
-        <v>0.05858202624828519</v>
+        <v>-0.1157432038956927</v>
       </c>
       <c r="FI12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ12" t="n">
-        <v>-0.06805950009083772</v>
+        <v>0.06635283760563254</v>
       </c>
       <c r="FK12" t="n">
-        <v>0.01191206852919623</v>
+        <v>0.034154642996314</v>
       </c>
       <c r="FL12" t="n">
         <v>-0</v>
@@ -7202,52 +7202,52 @@
         <v>-0</v>
       </c>
       <c r="FP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>-5.680465824922228e-05</v>
+        <v>-0.06709211346190208</v>
       </c>
       <c r="FR12" t="n">
         <v>-0</v>
       </c>
       <c r="FS12" t="n">
-        <v>-0.04101552251145823</v>
+        <v>0.2731943899873181</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.002162994002623726</v>
+        <v>0.02799095883474396</v>
       </c>
       <c r="FU12" t="n">
         <v>0</v>
       </c>
       <c r="FV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY12" t="n">
         <v>0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>-0.007807666853151745</v>
+        <v>-0.1109737817049804</v>
       </c>
       <c r="GA12" t="n">
         <v>0</v>
       </c>
       <c r="GB12" t="n">
-        <v>0.03177033084526919</v>
+        <v>0.02878171698089176</v>
       </c>
       <c r="GC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD12" t="n">
         <v>0</v>
       </c>
       <c r="GE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF12" t="n">
         <v>-0</v>
@@ -7258,49 +7258,49 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B13" t="n">
-        <v>1.080813607114461</v>
+        <v>0.4304746638372586</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.6388179300322536</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.2310823830360153</v>
+        <v>0.08496607535051609</v>
       </c>
       <c r="F13" t="n">
-        <v>-0</v>
+        <v>-0.3376946423137124</v>
       </c>
       <c r="G13" t="n">
         <v>-0</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.8242953839875931</v>
+        <v>0.4633300245011933</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.461096051473259</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.1803695431258359</v>
+        <v>-0.09100901359785432</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>-0.3309313757200087</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -7309,109 +7309,109 @@
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2125816952022466</v>
+        <v>0.1304488488913219</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.02606108610083013</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0.1263141620409324</v>
+        <v>-0.02461748409873438</v>
       </c>
       <c r="X13" t="n">
-        <v>-0</v>
+        <v>-0.1774979949116219</v>
       </c>
       <c r="Y13" t="n">
         <v>-0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB13" t="n">
         <v>-0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.2115368195234953</v>
+        <v>-0.06432068296602564</v>
       </c>
       <c r="AD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0.05479161189608589</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.02595546506508219</v>
+        <v>-0.1979611108817287</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>0.04837142395109821</v>
       </c>
       <c r="AH13" t="n">
         <v>-0</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.1098970862084568</v>
+        <v>0.1476119435429731</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN13" t="n">
-        <v>-0.09318920283338135</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>-0.0855050891522502</v>
+        <v>0.04376293283858327</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>-0.08677609950390687</v>
       </c>
       <c r="AQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS13" t="n">
         <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.4790790986031287</v>
+        <v>0.4573773690412262</v>
       </c>
       <c r="AV13" t="n">
         <v>-0</v>
       </c>
       <c r="AW13" t="n">
-        <v>-0.1592357350461922</v>
+        <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.1271264185789649</v>
+        <v>-0.07631002693229003</v>
       </c>
       <c r="AY13" t="n">
-        <v>-0</v>
+        <v>-0.1841183408071357</v>
       </c>
       <c r="AZ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA13" t="n">
         <v>-0</v>
@@ -7420,76 +7420,76 @@
         <v>-0</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.2278927918815214</v>
+        <v>-0.1646976561831535</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF13" t="n">
-        <v>-0.1653770171235002</v>
+        <v>-0</v>
       </c>
       <c r="BG13" t="n">
-        <v>-0.3368390781902624</v>
+        <v>-0.04574458015411505</v>
       </c>
       <c r="BH13" t="n">
-        <v>-0</v>
+        <v>-0.008573550952340378</v>
       </c>
       <c r="BI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK13" t="n">
         <v>-0</v>
       </c>
       <c r="BL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.1187295425944058</v>
+        <v>0.00887985412911787</v>
       </c>
       <c r="BN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.1149732936320968</v>
+        <v>-0</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.08764190689336275</v>
+        <v>0.1339472497965222</v>
       </c>
       <c r="BQ13" t="n">
-        <v>-0</v>
+        <v>0.1098294016945471</v>
       </c>
       <c r="BR13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS13" t="n">
         <v>-0</v>
       </c>
       <c r="BT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU13" t="n">
         <v>-0</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.3287292281338971</v>
+        <v>0.3507182804261266</v>
       </c>
       <c r="BW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX13" t="n">
-        <v>-0.1631851468083467</v>
+        <v>0</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.1165734954721135</v>
+        <v>-0.0258473803684874</v>
       </c>
       <c r="BZ13" t="n">
-        <v>-0</v>
+        <v>-0.2336074755285877</v>
       </c>
       <c r="CA13" t="n">
         <v>-0</v>
@@ -7498,58 +7498,58 @@
         <v>-0</v>
       </c>
       <c r="CC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD13" t="n">
         <v>-0</v>
       </c>
       <c r="CE13" t="n">
-        <v>-0.1669406295200661</v>
+        <v>-0.1549121307124181</v>
       </c>
       <c r="CF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG13" t="n">
-        <v>0.09393093818909273</v>
+        <v>-0</v>
       </c>
       <c r="CH13" t="n">
-        <v>-0.02631547338774122</v>
+        <v>0.04229534404731442</v>
       </c>
       <c r="CI13" t="n">
-        <v>0</v>
+        <v>0.1140126442604278</v>
       </c>
       <c r="CJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK13" t="n">
         <v>0</v>
       </c>
       <c r="CL13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN13" t="n">
-        <v>0.1437057231125689</v>
+        <v>-0.1126243884926442</v>
       </c>
       <c r="CO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP13" t="n">
-        <v>-0.184002471729287</v>
+        <v>-0</v>
       </c>
       <c r="CQ13" t="n">
-        <v>-0.3090697995301707</v>
+        <v>0.2207314955097378</v>
       </c>
       <c r="CR13" t="n">
-        <v>0</v>
+        <v>0.03951588227339561</v>
       </c>
       <c r="CS13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU13" t="n">
         <v>0</v>
@@ -7558,19 +7558,19 @@
         <v>0</v>
       </c>
       <c r="CW13" t="n">
-        <v>-0.1672137274031648</v>
+        <v>-0.1413871964465885</v>
       </c>
       <c r="CX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY13" t="n">
-        <v>0.1311033222632075</v>
+        <v>0</v>
       </c>
       <c r="CZ13" t="n">
-        <v>-0.03878469316115801</v>
+        <v>0.06132671180955271</v>
       </c>
       <c r="DA13" t="n">
-        <v>0</v>
+        <v>0.1376610498288481</v>
       </c>
       <c r="DB13" t="n">
         <v>0</v>
@@ -7579,25 +7579,25 @@
         <v>0</v>
       </c>
       <c r="DD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE13" t="n">
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>-0.1788621728977197</v>
+        <v>-0.04682155901889619</v>
       </c>
       <c r="DG13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.2392936285568136</v>
+        <v>-0</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.01863374074122489</v>
+        <v>-0.0496561468764642</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0</v>
+        <v>0.03925233381475958</v>
       </c>
       <c r="DK13" t="n">
         <v>0</v>
@@ -7612,19 +7612,19 @@
         <v>-0</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.07065279096539753</v>
+        <v>0.03757228890376949</v>
       </c>
       <c r="DP13" t="n">
         <v>0</v>
       </c>
       <c r="DQ13" t="n">
-        <v>-0.1324775833890767</v>
+        <v>-0</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.03091581478032441</v>
+        <v>-0.03531074339406828</v>
       </c>
       <c r="DS13" t="n">
-        <v>0</v>
+        <v>0.1449286323148171</v>
       </c>
       <c r="DT13" t="n">
         <v>-0</v>
@@ -7636,22 +7636,22 @@
         <v>0</v>
       </c>
       <c r="DW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX13" t="n">
-        <v>-0.06010221414864032</v>
+        <v>-0.0481395589421782</v>
       </c>
       <c r="DY13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ13" t="n">
-        <v>-0.1357660787470282</v>
+        <v>0</v>
       </c>
       <c r="EA13" t="n">
-        <v>-0.06301509786068137</v>
+        <v>0.03604188322017832</v>
       </c>
       <c r="EB13" t="n">
-        <v>0</v>
+        <v>-0.1257266172209583</v>
       </c>
       <c r="EC13" t="n">
         <v>0</v>
@@ -7663,22 +7663,22 @@
         <v>-0</v>
       </c>
       <c r="EF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG13" t="n">
-        <v>-0.1469080734876818</v>
+        <v>-0.06748559933880947</v>
       </c>
       <c r="EH13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI13" t="n">
-        <v>0.1583090213014456</v>
+        <v>-0</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.04813018883278779</v>
+        <v>0.03264464542820814</v>
       </c>
       <c r="EK13" t="n">
-        <v>-0</v>
+        <v>0.02280126287285232</v>
       </c>
       <c r="EL13" t="n">
         <v>-0</v>
@@ -7687,31 +7687,31 @@
         <v>-0</v>
       </c>
       <c r="EN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP13" t="n">
-        <v>-0.2051371569509174</v>
+        <v>-0.05119195800945776</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER13" t="n">
-        <v>0.08136004737449937</v>
+        <v>-0</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.08150125979027323</v>
+        <v>-0.1073803689443267</v>
       </c>
       <c r="ET13" t="n">
-        <v>-0</v>
+        <v>-0.07147793446289318</v>
       </c>
       <c r="EU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW13" t="n">
         <v>-0</v>
@@ -7720,49 +7720,49 @@
         <v>-0</v>
       </c>
       <c r="EY13" t="n">
-        <v>-0.1701514417336396</v>
+        <v>-0.1484815550836852</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA13" t="n">
-        <v>0.125872612410426</v>
+        <v>-0</v>
       </c>
       <c r="FB13" t="n">
-        <v>-0.03656584888520035</v>
+        <v>0.003168564349207409</v>
       </c>
       <c r="FC13" t="n">
-        <v>-0</v>
+        <v>0.1314087085126121</v>
       </c>
       <c r="FD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE13" t="n">
         <v>0</v>
       </c>
       <c r="FF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH13" t="n">
-        <v>0.01133716039506538</v>
+        <v>-0.1660371501648054</v>
       </c>
       <c r="FI13" t="n">
         <v>0</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0.1501876952161902</v>
+        <v>-0</v>
       </c>
       <c r="FK13" t="n">
-        <v>-0.06997946027151164</v>
+        <v>0.03713381089690269</v>
       </c>
       <c r="FL13" t="n">
-        <v>-0</v>
+        <v>0.1353086165719869</v>
       </c>
       <c r="FM13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN13" t="n">
         <v>0</v>
@@ -7771,22 +7771,22 @@
         <v>0</v>
       </c>
       <c r="FP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ13" t="n">
-        <v>-0.01550772374713432</v>
+        <v>-0.1195673021082305</v>
       </c>
       <c r="FR13" t="n">
         <v>-0</v>
       </c>
       <c r="FS13" t="n">
-        <v>-0.08354662527224266</v>
+        <v>-0</v>
       </c>
       <c r="FT13" t="n">
-        <v>-0.08212474714146493</v>
+        <v>-0.06591892577513406</v>
       </c>
       <c r="FU13" t="n">
-        <v>-0</v>
+        <v>-1.581985323170343e-05</v>
       </c>
       <c r="FV13" t="n">
         <v>-0</v>
@@ -7795,31 +7795,31 @@
         <v>0</v>
       </c>
       <c r="FX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.06595113395304074</v>
+        <v>-0.05131936941653443</v>
       </c>
       <c r="GA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB13" t="n">
-        <v>-0.07759028649511872</v>
+        <v>0</v>
       </c>
       <c r="GC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD13" t="n">
-        <v>-0</v>
+        <v>0.1260310605040258</v>
       </c>
       <c r="GE13" t="n">
         <v>-0</v>
       </c>
       <c r="GF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG13" t="n">
         <v>-0</v>
@@ -7827,19 +7827,19 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.4257616610717377</v>
+        <v>0</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.4420069806825139</v>
       </c>
       <c r="C14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1082017115188057</v>
+        <v>-0.2363167972615635</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.3309645966541649</v>
+        <v>0.1341426648698484</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -7854,19 +7854,19 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0.4275630372516828</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>0.3976947881565496</v>
       </c>
       <c r="L14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0.01468731618130306</v>
+        <v>-0.2769117791177056</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.2809343660846997</v>
+        <v>0.04611525216462665</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -7875,25 +7875,25 @@
         <v>-0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0.00739338461432903</v>
+        <v>-0</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>0.07512237817243596</v>
       </c>
       <c r="U14" t="n">
         <v>-0</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.02715173422414793</v>
+        <v>0.005019929095442235</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.02910855167630226</v>
+        <v>-0.002761559666567718</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -7902,31 +7902,31 @@
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.04844287443411974</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>-0</v>
+        <v>0.0002723092547039661</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>-0.02978636010763133</v>
+        <v>-0.1635046203707994</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.04512496270784996</v>
+        <v>0.06288315990473385</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -7935,19 +7935,19 @@
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.08108839581534227</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>0.07625313519480947</v>
       </c>
       <c r="AM14" t="n">
         <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.03510927020859651</v>
+        <v>-0.09719076469430835</v>
       </c>
       <c r="AO14" t="n">
-        <v>-0.1292302615496381</v>
+        <v>0.1224291776809789</v>
       </c>
       <c r="AP14" t="n">
         <v>0</v>
@@ -7956,58 +7956,58 @@
         <v>-0</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS14" t="n">
         <v>-0</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.2702105366376609</v>
+        <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>0.1986688078959179</v>
       </c>
       <c r="AV14" t="n">
         <v>-0</v>
       </c>
       <c r="AW14" t="n">
-        <v>-0.07274354026802779</v>
+        <v>-0.1719661028287215</v>
       </c>
       <c r="AX14" t="n">
-        <v>-0.1952802391957316</v>
+        <v>-0.0990456599242078</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ14" t="n">
         <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB14" t="n">
         <v>-0</v>
       </c>
       <c r="BC14" t="n">
-        <v>0.08607109929951978</v>
+        <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>-0.005846301789259311</v>
       </c>
       <c r="BE14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>-0.07074479543685872</v>
+        <v>-0.04919642766299961</v>
       </c>
       <c r="BG14" t="n">
-        <v>-0.05147181128632946</v>
+        <v>0.04576208855144649</v>
       </c>
       <c r="BH14" t="n">
         <v>0</v>
       </c>
       <c r="BI14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ14" t="n">
         <v>0</v>
@@ -8016,19 +8016,19 @@
         <v>0</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.05597345834230676</v>
+        <v>-0</v>
       </c>
       <c r="BM14" t="n">
-        <v>0</v>
+        <v>-0.1320732284569585</v>
       </c>
       <c r="BN14" t="n">
         <v>-0</v>
       </c>
       <c r="BO14" t="n">
-        <v>-0.01835924775684196</v>
+        <v>-0.01843869556423564</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.01299024579967883</v>
+        <v>-0.06215876483012147</v>
       </c>
       <c r="BQ14" t="n">
         <v>-0</v>
@@ -8040,25 +8040,25 @@
         <v>0</v>
       </c>
       <c r="BT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU14" t="n">
-        <v>0.1211234984847693</v>
+        <v>0</v>
       </c>
       <c r="BV14" t="n">
-        <v>0</v>
+        <v>0.2168691990972099</v>
       </c>
       <c r="BW14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX14" t="n">
-        <v>-0.02174089234791662</v>
+        <v>-0.09985605730877822</v>
       </c>
       <c r="BY14" t="n">
-        <v>-0.1002929914858199</v>
+        <v>-0.01211155114195133</v>
       </c>
       <c r="BZ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA14" t="n">
         <v>-0</v>
@@ -8067,22 +8067,22 @@
         <v>0</v>
       </c>
       <c r="CC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD14" t="n">
-        <v>-0.07497646336418853</v>
+        <v>-0</v>
       </c>
       <c r="CE14" t="n">
-        <v>0</v>
+        <v>-0.1433703759088884</v>
       </c>
       <c r="CF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG14" t="n">
-        <v>-0.005004027165343361</v>
+        <v>0.1330264315548192</v>
       </c>
       <c r="CH14" t="n">
-        <v>0.06226072682859271</v>
+        <v>-0.03792464633528538</v>
       </c>
       <c r="CI14" t="n">
         <v>-0</v>
@@ -8094,52 +8094,52 @@
         <v>0</v>
       </c>
       <c r="CL14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM14" t="n">
-        <v>0.008300025335779325</v>
+        <v>0</v>
       </c>
       <c r="CN14" t="n">
-        <v>0</v>
+        <v>-0.01319673978547366</v>
       </c>
       <c r="CO14" t="n">
         <v>-0</v>
       </c>
       <c r="CP14" t="n">
-        <v>0.01880248869164073</v>
+        <v>0.3140244859427735</v>
       </c>
       <c r="CQ14" t="n">
-        <v>-0.01906114851947478</v>
+        <v>0.1169186877096618</v>
       </c>
       <c r="CR14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS14" t="n">
         <v>-0</v>
       </c>
       <c r="CT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU14" t="n">
         <v>-0</v>
       </c>
       <c r="CV14" t="n">
-        <v>-0.06432416894671389</v>
+        <v>-0</v>
       </c>
       <c r="CW14" t="n">
-        <v>-0</v>
+        <v>-0.1374820776829288</v>
       </c>
       <c r="CX14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY14" t="n">
-        <v>0.002335864987961563</v>
+        <v>0.1286352027807182</v>
       </c>
       <c r="CZ14" t="n">
-        <v>0.07763007106269895</v>
+        <v>-0.02282755113215836</v>
       </c>
       <c r="DA14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB14" t="n">
         <v>-0</v>
@@ -8148,22 +8148,22 @@
         <v>-0</v>
       </c>
       <c r="DD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE14" t="n">
-        <v>-0.005203528650572919</v>
+        <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>-0</v>
+        <v>-0.05658545510563655</v>
       </c>
       <c r="DG14" t="n">
         <v>0</v>
       </c>
       <c r="DH14" t="n">
-        <v>0.107132785690349</v>
+        <v>0.03770703089404289</v>
       </c>
       <c r="DI14" t="n">
-        <v>-0.05999476426565549</v>
+        <v>-0.04212257467431451</v>
       </c>
       <c r="DJ14" t="n">
         <v>-0</v>
@@ -8178,19 +8178,19 @@
         <v>0</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.002580781124315811</v>
+        <v>0</v>
       </c>
       <c r="DO14" t="n">
-        <v>-0</v>
+        <v>0.0469675561539886</v>
       </c>
       <c r="DP14" t="n">
         <v>-0</v>
       </c>
       <c r="DQ14" t="n">
-        <v>0.01682913347502331</v>
+        <v>0.05339593242511024</v>
       </c>
       <c r="DR14" t="n">
-        <v>0.04841272533937082</v>
+        <v>0.05013045523361593</v>
       </c>
       <c r="DS14" t="n">
         <v>-0</v>
@@ -8199,31 +8199,31 @@
         <v>-0</v>
       </c>
       <c r="DU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV14" t="n">
         <v>0</v>
       </c>
       <c r="DW14" t="n">
-        <v>-0.0142498215469798</v>
+        <v>-0</v>
       </c>
       <c r="DX14" t="n">
-        <v>0</v>
+        <v>0.02529560155539401</v>
       </c>
       <c r="DY14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ14" t="n">
-        <v>-0.02237491541389057</v>
+        <v>-0.02507623630507313</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.0862431173137022</v>
+        <v>-0.03611475026149931</v>
       </c>
       <c r="EB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED14" t="n">
         <v>0</v>
@@ -8232,73 +8232,73 @@
         <v>-0</v>
       </c>
       <c r="EF14" t="n">
-        <v>-0.0805504230665354</v>
+        <v>-0</v>
       </c>
       <c r="EG14" t="n">
-        <v>0</v>
+        <v>-0.1367869248765865</v>
       </c>
       <c r="EH14" t="n">
         <v>0</v>
       </c>
       <c r="EI14" t="n">
-        <v>0.05593328653517852</v>
+        <v>0.1113169070909712</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.07400717473791005</v>
+        <v>0.007993480355575977</v>
       </c>
       <c r="EK14" t="n">
         <v>0</v>
       </c>
       <c r="EL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM14" t="n">
         <v>0</v>
       </c>
       <c r="EN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO14" t="n">
-        <v>-0.07079474968624892</v>
+        <v>-0</v>
       </c>
       <c r="EP14" t="n">
-        <v>0</v>
+        <v>-0.1437355272745666</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER14" t="n">
-        <v>-0.01723991064522254</v>
+        <v>0.05572593260486432</v>
       </c>
       <c r="ES14" t="n">
-        <v>0.01814936731622246</v>
+        <v>-0.01298102988329963</v>
       </c>
       <c r="ET14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU14" t="n">
         <v>0</v>
       </c>
       <c r="EV14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX14" t="n">
-        <v>-0.06093308062219609</v>
+        <v>-0</v>
       </c>
       <c r="EY14" t="n">
-        <v>0</v>
+        <v>-0.1621901293583886</v>
       </c>
       <c r="EZ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA14" t="n">
-        <v>-0.006754780045409122</v>
+        <v>0.153762757467637</v>
       </c>
       <c r="FB14" t="n">
-        <v>0.05808291851943752</v>
+        <v>-0.04690309235116157</v>
       </c>
       <c r="FC14" t="n">
         <v>-0</v>
@@ -8313,25 +8313,25 @@
         <v>-0</v>
       </c>
       <c r="FG14" t="n">
-        <v>-0.008274235148020509</v>
+        <v>0</v>
       </c>
       <c r="FH14" t="n">
-        <v>0</v>
+        <v>-0.1060530695158781</v>
       </c>
       <c r="FI14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.04671787264454726</v>
+        <v>0.1424047264688722</v>
       </c>
       <c r="FK14" t="n">
-        <v>0.07973460684251754</v>
+        <v>-0.06603738104009008</v>
       </c>
       <c r="FL14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN14" t="n">
         <v>0</v>
@@ -8340,58 +8340,627 @@
         <v>-0</v>
       </c>
       <c r="FP14" t="n">
-        <v>-0.04533573567904512</v>
+        <v>0</v>
       </c>
       <c r="FQ14" t="n">
-        <v>-0</v>
+        <v>-0.1577622601592216</v>
       </c>
       <c r="FR14" t="n">
         <v>-0</v>
       </c>
       <c r="FS14" t="n">
-        <v>-0.0008660072611884913</v>
+        <v>-0.08284660483260876</v>
       </c>
       <c r="FT14" t="n">
-        <v>0.1071565473790611</v>
+        <v>-0.004087093432489895</v>
       </c>
       <c r="FU14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV14" t="n">
         <v>0</v>
       </c>
       <c r="FW14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY14" t="n">
-        <v>0.02631571511629985</v>
+        <v>0</v>
       </c>
       <c r="FZ14" t="n">
-        <v>-0</v>
+        <v>-0.1263080464641067</v>
       </c>
       <c r="GA14" t="n">
         <v>0</v>
       </c>
       <c r="GB14" t="n">
-        <v>0.06824294513463973</v>
+        <v>0.09326009086393669</v>
       </c>
       <c r="GC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD14" t="n">
         <v>0</v>
       </c>
       <c r="GE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG14" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>0.1156907614773899</v>
+      </c>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.2006515208334778</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.1911800589288066</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.06774072133878981</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>-0.2279600023120652</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.1273004100958638</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>-0.04224777554333293</v>
+      </c>
+      <c r="T15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>-0.03503660775045954</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.03817035801026335</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.09548744433116504</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0.0709634557255362</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0.1570601333758321</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>-0.03158727887622501</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>-0.0702696231529772</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0.08602959470089427</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>-0.1058278189005517</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>-0.2409177510668015</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0.002813348792911753</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0.05702732022774426</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>0.1503897238894905</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>0.0881718833890503</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>-0.02342919926043045</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>0.0171799362541298</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>-0.1247763044167371</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>-0.1053554277519105</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>-0.2800340058969704</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>-0.03129469427991509</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD15" t="n">
+        <v>-0.06188666954304771</v>
+      </c>
+      <c r="CE15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG15" t="n">
+        <v>0.1108057775306569</v>
+      </c>
+      <c r="CH15" t="n">
+        <v>-0.04546380365191277</v>
+      </c>
+      <c r="CI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>0.07821448243084496</v>
+      </c>
+      <c r="CN15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CO15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP15" t="n">
+        <v>0.2699558146330842</v>
+      </c>
+      <c r="CQ15" t="n">
+        <v>0.05359366779784927</v>
+      </c>
+      <c r="CR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV15" t="n">
+        <v>-0.0543165487434546</v>
+      </c>
+      <c r="CW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CY15" t="n">
+        <v>0.1201109553781808</v>
+      </c>
+      <c r="CZ15" t="n">
+        <v>-0.04819869339427515</v>
+      </c>
+      <c r="DA15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DB15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE15" t="n">
+        <v>0.005282620708447268</v>
+      </c>
+      <c r="DF15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH15" t="n">
+        <v>0.1036714807500619</v>
+      </c>
+      <c r="DI15" t="n">
+        <v>-0.03557787843167359</v>
+      </c>
+      <c r="DJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN15" t="n">
+        <v>0.01902932716645124</v>
+      </c>
+      <c r="DO15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ15" t="n">
+        <v>0.03830948562161484</v>
+      </c>
+      <c r="DR15" t="n">
+        <v>0.03947017507539673</v>
+      </c>
+      <c r="DS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW15" t="n">
+        <v>0.01122152363396879</v>
+      </c>
+      <c r="DX15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DY15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ15" t="n">
+        <v>0.004287858123581964</v>
+      </c>
+      <c r="EA15" t="n">
+        <v>-0.04160320110645537</v>
+      </c>
+      <c r="EB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF15" t="n">
+        <v>-0.1205305236386903</v>
+      </c>
+      <c r="EG15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI15" t="n">
+        <v>0.1045168029085235</v>
+      </c>
+      <c r="EJ15" t="n">
+        <v>-0.002258668313713617</v>
+      </c>
+      <c r="EK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO15" t="n">
+        <v>0.01185455946260621</v>
+      </c>
+      <c r="EP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER15" t="n">
+        <v>0.1078460273468946</v>
+      </c>
+      <c r="ES15" t="n">
+        <v>-0.01904038449138782</v>
+      </c>
+      <c r="ET15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX15" t="n">
+        <v>-0.05964226150797309</v>
+      </c>
+      <c r="EY15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA15" t="n">
+        <v>0.155425716020596</v>
+      </c>
+      <c r="FB15" t="n">
+        <v>-0.02633069427963618</v>
+      </c>
+      <c r="FC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG15" t="n">
+        <v>-0.04844575003386006</v>
+      </c>
+      <c r="FH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ15" t="n">
+        <v>0.1547705136562491</v>
+      </c>
+      <c r="FK15" t="n">
+        <v>-0.02521880245235584</v>
+      </c>
+      <c r="FL15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP15" t="n">
+        <v>-0.01174381614535415</v>
+      </c>
+      <c r="FQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS15" t="n">
+        <v>0.2721736596114886</v>
+      </c>
+      <c r="FT15" t="n">
+        <v>-0.02236640164875315</v>
+      </c>
+      <c r="FU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY15" t="n">
+        <v>-0.02148766594963532</v>
+      </c>
+      <c r="FZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GB15" t="n">
+        <v>0.1131093517526573</v>
+      </c>
+      <c r="GC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GE15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG15" t="n">
+        <v>-0</v>
       </c>
     </row>
   </sheetData>
